--- a/links/Juegos_WII U.xlsx
+++ b/links/Juegos_WII U.xlsx
@@ -397,14 +397,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AP41"/>
+  <dimension ref="A1:AG81"/>
   <cols>
     <col min="1" max="1" width="45.83203125" customWidth="1"/>
     <col min="2" max="2" width="45.83203125" customWidth="1"/>
     <col min="3" max="3" width="45.83203125" customWidth="1"/>
     <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="35.83203125" customWidth="1"/>
+    <col min="5" max="5" width="50.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
     <col min="7" max="7" width="35.83203125" customWidth="1"/>
     <col min="8" max="8" width="35.83203125" customWidth="1"/>
     <col min="9" max="9" width="35.83203125" customWidth="1"/>
@@ -432,15 +432,6 @@
     <col min="31" max="31" width="35.83203125" customWidth="1"/>
     <col min="32" max="32" width="35.83203125" customWidth="1"/>
     <col min="33" max="33" width="35.83203125" customWidth="1"/>
-    <col min="34" max="34" width="35.83203125" customWidth="1"/>
-    <col min="35" max="35" width="35.83203125" customWidth="1"/>
-    <col min="36" max="36" width="35.83203125" customWidth="1"/>
-    <col min="37" max="37" width="35.83203125" customWidth="1"/>
-    <col min="38" max="38" width="35.83203125" customWidth="1"/>
-    <col min="39" max="39" width="35.83203125" customWidth="1"/>
-    <col min="40" max="40" width="35.83203125" customWidth="1"/>
-    <col min="41" max="41" width="35.83203125" customWidth="1"/>
-    <col min="42" max="42" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -457,79 +448,79 @@
         <v>Imagen Local</v>
       </c>
       <c r="E1" t="str">
+        <v>Sinopsis</v>
+      </c>
+      <c r="F1" t="str">
         <v>En Varias Partes</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Mega</v>
       </c>
-      <c r="G1" t="str">
-        <v>Mega Parte 1</v>
-      </c>
       <c r="H1" t="str">
-        <v>Mega Parte 2</v>
+        <v>1Fichier</v>
       </c>
       <c r="I1" t="str">
-        <v>Mega Parte 3</v>
+        <v>Otro Link 1</v>
       </c>
       <c r="J1" t="str">
-        <v>Mega Parte 4</v>
+        <v>Otro Link 2</v>
       </c>
       <c r="K1" t="str">
-        <v>Mega Parte 5</v>
+        <v>Otro Link 3</v>
       </c>
       <c r="L1" t="str">
-        <v>Mega Parte 6</v>
+        <v>Otro Link 4</v>
       </c>
       <c r="M1" t="str">
+        <v>Otro Link 5</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Otro Link 6</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Megaup</v>
+      </c>
+      <c r="P1" t="str">
         <v>Mediafire</v>
       </c>
-      <c r="N1" t="str">
-        <v>Mediafire Parte 1</v>
-      </c>
-      <c r="O1" t="str">
-        <v>Mediafire Parte 2</v>
-      </c>
-      <c r="P1" t="str">
-        <v>1Fichier</v>
-      </c>
       <c r="Q1" t="str">
+        <v>Otro Link 7</v>
+      </c>
+      <c r="R1" t="str">
+        <v>Otro Link 8</v>
+      </c>
+      <c r="S1" t="str">
+        <v>Otro Link 9</v>
+      </c>
+      <c r="T1" t="str">
+        <v>Google Drive</v>
+      </c>
+      <c r="U1" t="str">
+        <v>Google Drive Parte 1</v>
+      </c>
+      <c r="V1" t="str">
+        <v>Google Drive Parte 2</v>
+      </c>
+      <c r="W1" t="str">
         <v>1Fichier Parte 1</v>
       </c>
-      <c r="R1" t="str">
+      <c r="X1" t="str">
         <v>1Fichier Parte 2</v>
       </c>
-      <c r="S1" t="str">
+      <c r="Y1" t="str">
         <v>1Fichier Parte 3</v>
       </c>
-      <c r="T1" t="str">
+      <c r="Z1" t="str">
         <v>1Fichier Parte 4</v>
       </c>
-      <c r="U1" t="str">
+      <c r="AA1" t="str">
         <v>1Fichier Parte 5</v>
       </c>
-      <c r="V1" t="str">
+      <c r="AB1" t="str">
         <v>1Fichier Parte 6</v>
       </c>
-      <c r="W1" t="str">
-        <v>Google Drive</v>
-      </c>
-      <c r="X1" t="str">
-        <v>Google Drive Parte 1</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>Google Drive Parte 2</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>Google Drive Parte 3</v>
-      </c>
-      <c r="AA1" t="str">
-        <v>Qiwi</v>
-      </c>
-      <c r="AB1" t="str">
-        <v>Pixeldrain</v>
-      </c>
       <c r="AC1" t="str">
-        <v>Megaup</v>
+        <v>1Fichier Parte 7</v>
       </c>
       <c r="AD1" t="str">
         <v>Megaup Parte 1</v>
@@ -538,37 +529,10 @@
         <v>Megaup Parte 2</v>
       </c>
       <c r="AF1" t="str">
-        <v>Megaup Parte 3</v>
+        <v>Mega Parte 1</v>
       </c>
       <c r="AG1" t="str">
-        <v>Megaup Parte 4</v>
-      </c>
-      <c r="AH1" t="str">
-        <v>Otro Link 1</v>
-      </c>
-      <c r="AI1" t="str">
-        <v>Otro Link 2</v>
-      </c>
-      <c r="AJ1" t="str">
-        <v>Otro Link 3</v>
-      </c>
-      <c r="AK1" t="str">
-        <v>Otro Link 4</v>
-      </c>
-      <c r="AL1" t="str">
-        <v>Otro Link 5</v>
-      </c>
-      <c r="AM1" t="str">
-        <v>Otro Link 6</v>
-      </c>
-      <c r="AN1" t="str">
-        <v>Otro Link 7</v>
-      </c>
-      <c r="AO1" t="str">
-        <v>Otro Link 8</v>
-      </c>
-      <c r="AP1" t="str">
-        <v>Otro Link 9</v>
+        <v>Mega Parte 2</v>
       </c>
     </row>
     <row r="2">
@@ -585,24 +549,27 @@
         <v>imagenes/WII U/Fast Racing NEO.jpg</v>
       </c>
       <c r="E2" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F2" t="str">
+        <v>No</v>
+      </c>
+      <c r="G2" t="str">
         <v>https://mega.nz/#!PL4C2ChD!Xx7ZhMmY1n_bpP8YToYyZRmyugrzJMiyaFM3733mokE</v>
       </c>
-      <c r="P2" t="str">
+      <c r="H2" t="str">
         <v>https://1fichier.com/?p111mn76iu&amp;af=62851</v>
       </c>
-      <c r="AH2" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AI2" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AJ2" t="str">
+      <c r="I2" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J2" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K2" t="str">
         <v>https://www.filecrypt.cc/Container/D8346B80EA.html: https://www.filecrypt.cc/Container/D8346B80EA.html</v>
       </c>
-      <c r="AK2" t="str">
+      <c r="L2" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -620,51 +587,21 @@
         <v>imagenes/WII U/ZombiU.jpg</v>
       </c>
       <c r="E3" t="str">
-        <v>No</v>
-      </c>
-      <c r="G3" t="str">
-        <v>https://mega.nz/file/lmgzgIYI#4O2GNMqBQ9dujiNtzYrwWmZWUr96u-N96gAv3rWw9AE</v>
-      </c>
-      <c r="H3" t="str">
-        <v>https://mega.nz/file/kjAGESrI#1q0Vjq7yvp-dk4rGMhESuxHyxQ4Q1hiDHfO1MNUEKP8</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F3" t="str">
+        <v>No</v>
       </c>
       <c r="I3" t="str">
-        <v>https://mega.nz/file/17oXSZJA#wQJbRd_xpgEIGPtXrElGKbhg_BuOoCZalnjeDz5GNGc</v>
+        <v>https://nswgame.com/guide-download-game/</v>
       </c>
       <c r="J3" t="str">
-        <v>https://mega.nz/file/p3ZGiKRD#qF74RD4Nw2il6rZ6GOwXiuT-JVIWFtjWRtQpSDKsRCw</v>
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
       </c>
       <c r="K3" t="str">
-        <v>https://mega.nz/file/Zm5ACCLB#tdv0wJ5fo_sspUkYNkeLGyZ5voPQlU8ryEyINJREAzA</v>
+        <v>https://anotepad.com/notes/j4kghnxf: https://anotepad.com/notes/j4kghnxf</v>
       </c>
       <c r="L3" t="str">
-        <v>https://mega.nz/file/cE8jjCRZ#CslOFqQ7BZuAixtu88cnZsuVNcz9xLxeYYrlkSrO0tA: https://mega.nz/file/cE8jjCRZ#CslOFqQ7BZuAixtu88cnZsuVNcz9xLxeYYrlkSrO0tA</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>https://1fichier.com/?9dasrqsddv&amp;af=62851</v>
-      </c>
-      <c r="R3" t="str">
-        <v>https://1fichier.com/?lxl55yvlwh&amp;af=62851</v>
-      </c>
-      <c r="S3" t="str">
-        <v>https://1fichier.com/?z4fxv9kf2k&amp;af=62851</v>
-      </c>
-      <c r="T3" t="str">
-        <v>https://1fichier.com/?6su51lxbe4&amp;af=62851</v>
-      </c>
-      <c r="U3" t="str">
-        <v>https://1fichier.com/?er78uowt79&amp;af=62851</v>
-      </c>
-      <c r="AH3" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AI3" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AJ3" t="str">
-        <v>https://anotepad.com/notes/j4kghnxf: https://anotepad.com/notes/j4kghnxf</v>
-      </c>
-      <c r="AK3" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -682,60 +619,27 @@
         <v>imagenes/WII U/Yos﻿his Woolly World.jpg</v>
       </c>
       <c r="E4" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F4" t="str">
         <v>Sí</v>
       </c>
-      <c r="G4" t="str">
-        <v>https://www.filecrypt.cc/Container/1C04D52452.html</v>
-      </c>
-      <c r="H4" t="str">
-        <v>https://mega.nz/file/SHhRBCRT#IlyWVnabIcsfBIcnIFkwHFnwViV2oS1Iako5ZWUVFrg</v>
+      <c r="I4" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J4" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K4" t="str">
+        <v>https://send.cm/d/8pc4</v>
+      </c>
+      <c r="L4" t="str">
+        <v>https://send.cm/d/8pdJ</v>
+      </c>
+      <c r="M4" t="str">
+        <v>https://send.cm/d/8pdL</v>
       </c>
       <c r="N4" t="str">
-        <v>https://www.filecrypt.cc/Container/1FF425A900.html</v>
-      </c>
-      <c r="O4" t="str">
-        <v>https://www.mediafire.com/file/uc54knymkopm63d/Y-WW-EUR-LOADIINE-UPDATE-ZIPERTO.rar/file</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>https://www.filecrypt.cc/Container/FC70189F96.html</v>
-      </c>
-      <c r="R4" t="str">
-        <v>https://1fichier.com/?jcy6vytwa8yg5hsp09p9</v>
-      </c>
-      <c r="S4" t="str">
-        <v>https://1fichier.com/?l8uicaqtt0fyd5txsdyx&amp;af=62851</v>
-      </c>
-      <c r="T4" t="str">
-        <v>https://1fichier.com/?z8pv8a14tsbldcs91uyk&amp;af=62851</v>
-      </c>
-      <c r="U4" t="str">
-        <v>https://1fichier.com/?1vcgwx99vnx17w9ios4j&amp;af=62851</v>
-      </c>
-      <c r="AD4" t="str">
-        <v>https://megaup.net/12jzc/Y-WW-USA-LOADIINE-ZIPERTO.part1.rar</v>
-      </c>
-      <c r="AE4" t="str">
-        <v>https://megaup.net/2oevc/Y-WW-USA-LOADIINE-ZIPERTO.part2.rar</v>
-      </c>
-      <c r="AF4" t="str">
-        <v>https://megaup.net/2oern/Y-WW-USA-UPv32-LOADIINE-ZIPERTO.rar</v>
-      </c>
-      <c r="AH4" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AI4" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AJ4" t="str">
-        <v>https://send.cm/d/8pc4</v>
-      </c>
-      <c r="AK4" t="str">
-        <v>https://send.cm/d/8pdJ</v>
-      </c>
-      <c r="AL4" t="str">
-        <v>https://send.cm/d/8pdL</v>
-      </c>
-      <c r="AM4" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -753,40 +657,25 @@
         <v>imagenes/WII U/Xenoblade Chronicles X.jpg</v>
       </c>
       <c r="E5" t="str">
-        <v>No</v>
-      </c>
-      <c r="G5" t="str">
-        <v>https://filecrypt.cc/Container/FB803FFB42.html</v>
-      </c>
-      <c r="H5" t="str">
-        <v>https://mega.nz/file/9U5hCSzI#UJShKVuRrJtzISfcYEnKOSqmiVUTNDiqeGSUE3ZjP-U</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F5" t="str">
+        <v>No</v>
       </c>
       <c r="I5" t="str">
-        <v>https://www.filecrypt.cc/Container/82375F8737.html</v>
-      </c>
-      <c r="Q5" t="str">
-        <v>https://www.filecrypt.cc/Container/38E20243BF.html</v>
-      </c>
-      <c r="R5" t="str">
-        <v>https://1fichier.com/?kfbwsxmrwm84n3twmjd0</v>
-      </c>
-      <c r="S5" t="str">
-        <v>https://www.filecrypt.cc/Container/DCDB3FD334.html</v>
-      </c>
-      <c r="AC5" t="str">
+        <v>https://www.filecrypt.cc/Container/DB19BA77FE.html</v>
+      </c>
+      <c r="J5" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="K5" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="L5" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="O5" t="str">
         <v>https://www.filecrypt.cc/Container/7DE83835E7.html</v>
-      </c>
-      <c r="AH5" t="str">
-        <v>https://www.filecrypt.cc/Container/DB19BA77FE.html</v>
-      </c>
-      <c r="AI5" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AJ5" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AK5" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
     <row r="6">
@@ -803,24 +692,27 @@
         <v>imagenes/WII U/Wii Sports Club.jpg</v>
       </c>
       <c r="E6" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F6" t="str">
+        <v>No</v>
+      </c>
+      <c r="G6" t="str">
         <v>https://mega.nz/file/emwSzJLS#jN_zxRRwKGzRzhYbVXCdGUNteOXNSkGVWk2NI-LNhLw</v>
       </c>
-      <c r="P6" t="str">
+      <c r="H6" t="str">
         <v>https://1fichier.com/?svc59bnqz0&amp;af=62851</v>
       </c>
-      <c r="AH6" t="str">
+      <c r="I6" t="str">
         <v>https://docs.google.com/uc?id=0B0lnKSdJsB3dOHNJa0JCTjBuWEE&amp;export=download</v>
       </c>
-      <c r="AI6" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AJ6" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AK6" t="str">
+      <c r="J6" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="K6" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="L6" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -838,24 +730,27 @@
         <v>imagenes/WII U/Wii Party U.jpg</v>
       </c>
       <c r="E7" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F7" t="str">
         <v>Sí</v>
       </c>
-      <c r="AH7" t="str">
+      <c r="I7" t="str">
         <v>https://www.filecrypt.cc/Container/CCB06EBBAF.html</v>
       </c>
-      <c r="AI7" t="str">
+      <c r="J7" t="str">
         <v>https://www.filecrypt.cc/Container/70010B5D19.html</v>
       </c>
-      <c r="AJ7" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AK7" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AL7" t="str">
+      <c r="K7" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="L7" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="M7" t="str">
         <v>https://nswgame.com/running-fable-petite-party-nintendo-switch-nsp-xci-nsz-download-free/</v>
       </c>
-      <c r="AM7" t="str">
+      <c r="N7" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -873,25 +768,28 @@
         <v>imagenes/WII U/Wii Fit U.jpg</v>
       </c>
       <c r="E8" t="str">
-        <v>No</v>
-      </c>
-      <c r="M8" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F8" t="str">
+        <v>No</v>
+      </c>
+      <c r="H8" t="str">
+        <v>https://1fichier.com/?490g5a7606qppicgb8wa&amp;af=62851</v>
+      </c>
+      <c r="I8" t="str">
+        <v>https://send.cm/d/6Y6x</v>
+      </c>
+      <c r="J8" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="K8" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="L8" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="P8" t="str">
         <v>https://www.mediafire.com/file/sy3x4wr6z4zjl96/WF-U-USA-Loadiine-Ziperto.rar/file</v>
-      </c>
-      <c r="P8" t="str">
-        <v>https://1fichier.com/?490g5a7606qppicgb8wa&amp;af=62851</v>
-      </c>
-      <c r="AH8" t="str">
-        <v>https://send.cm/d/6Y6x</v>
-      </c>
-      <c r="AI8" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AJ8" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AK8" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
     <row r="9">
@@ -908,33 +806,30 @@
         <v>imagenes/WII U/Tokyo Mirage Sessions #FE.jpg</v>
       </c>
       <c r="E9" t="str">
-        <v>No</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F9" t="str">
+        <v>No</v>
+      </c>
+      <c r="I9" t="str">
+        <v>https://www.filecrypt.cc/Container/FCD0B54F2F.html</v>
+      </c>
+      <c r="J9" t="str">
+        <v>https://www.filecrypt.cc/Container/79A4EA5B4C.html</v>
+      </c>
+      <c r="K9" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="L9" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="M9" t="str">
+        <v>https://filecrypt.cc/Container/3156E4B63B.html</v>
+      </c>
+      <c r="N9" t="str">
+        <v>https://www.filecrypt.cc/Container/94F72F860B.html</v>
       </c>
       <c r="Q9" t="str">
-        <v>https://1fichier.com/?6pdo2aac868zq9la4ujt</v>
-      </c>
-      <c r="R9" t="str">
-        <v>https://1fichier.com/?pqlxf71nc854cl16seks</v>
-      </c>
-      <c r="AH9" t="str">
-        <v>https://www.filecrypt.cc/Container/FCD0B54F2F.html</v>
-      </c>
-      <c r="AI9" t="str">
-        <v>https://www.filecrypt.cc/Container/79A4EA5B4C.html</v>
-      </c>
-      <c r="AJ9" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AK9" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AL9" t="str">
-        <v>https://filecrypt.cc/Container/3156E4B63B.html</v>
-      </c>
-      <c r="AM9" t="str">
-        <v>https://www.filecrypt.cc/Container/94F72F860B.html</v>
-      </c>
-      <c r="AN9" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -952,24 +847,21 @@
         <v>imagenes/WII U/The Wond﻿erful 101.jpg</v>
       </c>
       <c r="E10" t="str">
-        <v>No</v>
-      </c>
-      <c r="Q10" t="str">
-        <v>https://1fichier.com/?o1x8gpk08hkl0sq54h2o</v>
-      </c>
-      <c r="R10" t="str">
-        <v>https://1fichier.com/?2uw4xec2nlsvt0zucivi</v>
-      </c>
-      <c r="AH10" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F10" t="str">
+        <v>No</v>
+      </c>
+      <c r="I10" t="str">
         <v>https://filecrypt.cc/Container/FF6E7A78A1.html</v>
       </c>
-      <c r="AI10" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AJ10" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AK10" t="str">
+      <c r="J10" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="K10" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="L10" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -987,21 +879,18 @@
         <v>imagenes/WII U/The LEGO Movie Videogame.jpg</v>
       </c>
       <c r="E11" t="str">
-        <v>No</v>
-      </c>
-      <c r="Q11" t="str">
-        <v>https://1fichier.com/?5e264rk9ecrsjrjzrrfr</v>
-      </c>
-      <c r="R11" t="str">
-        <v>https://1fichier.com/?s3zj9os6trkz9o6qodn2</v>
-      </c>
-      <c r="AH11" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AI11" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AJ11" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F11" t="str">
+        <v>No</v>
+      </c>
+      <c r="I11" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J11" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K11" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1019,33 +908,36 @@
         <v>imagenes/WII U/The Legend of Zelda Twilight Princess HD.jpg</v>
       </c>
       <c r="E12" t="str">
-        <v>No</v>
-      </c>
-      <c r="AH12" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F12" t="str">
+        <v>No</v>
+      </c>
+      <c r="I12" t="str">
         <v>https://www.filecrypt.cc/Container/22F7B6BD39.html</v>
       </c>
-      <c r="AI12" t="str">
+      <c r="J12" t="str">
         <v>https://www.filecrypt.cc/Container/746764E5E6.html</v>
       </c>
-      <c r="AJ12" t="str">
+      <c r="K12" t="str">
         <v>https://www.filecrypt.cc/Container/21B7C6475C.html</v>
       </c>
-      <c r="AK12" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AL12" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AM12" t="str">
+      <c r="L12" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="M12" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="N12" t="str">
         <v>https://www.filecrypt.cc/Container/689D9BE052.html</v>
       </c>
-      <c r="AN12" t="str">
+      <c r="Q12" t="str">
         <v>https://www.filecrypt.cc/Container/2454F35BB8.html</v>
       </c>
-      <c r="AO12" t="str">
+      <c r="R12" t="str">
         <v>https://www.filecrypt.cc/Container/026A301DF7.html</v>
       </c>
-      <c r="AP12" t="str">
+      <c r="S12" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1063,66 +955,24 @@
         <v>imagenes/WII U/The Legend of Zelda The Wind Waker HD.jpg</v>
       </c>
       <c r="E13" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F13" t="str">
         <v>Sí</v>
       </c>
-      <c r="G13" t="str">
-        <v>https://mega.nz/file/BjBA2S7K#zaodhHgfgvG1Tb-t47bUI7H_JJOKrz6nqwogQEoQGV0</v>
-      </c>
-      <c r="H13" t="str">
-        <v>https://mega.nz/file/lnZDyCCJ#_7z5lmVFdUU0BOukw7fXoIWHDgIszZm-OHoCmN6_U_g</v>
-      </c>
       <c r="I13" t="str">
-        <v>https://mega.nz/file/eo1wXIpa#IQoyABLHC5UgHADZ5MREf157YDQNsPYhFptrpvt9QIk</v>
+        <v>https://nswgame.com/guide-download-game/</v>
       </c>
       <c r="J13" t="str">
-        <v>https://mega.nz/file/G5tmXAhA#NPd3qCDADDmgDS2MY1iZ5XKKBSApzDyysnJ0WXStUb8</v>
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
       </c>
       <c r="K13" t="str">
-        <v>https://mega.nz/file/tuEmESrA#aDHHFnpHkGVtAMOuIJZ3Nm0vJRB_33S3fDiKuHrq9HM</v>
-      </c>
-      <c r="N13" t="str">
-        <v>https://www.mediafire.com/file/z7qz67jkuet4kq4/TLOZ-TWW-HD-EUR-LOADIINE-ZIPERTO.part1.rar/file</v>
-      </c>
-      <c r="O13" t="str">
-        <v>https://www.mediafire.com/file/gw4xgdvp098ycuq/TLOZ-TWW-HD-EUR-LOADIINE-ZIPERTO.part2.rar/file</v>
-      </c>
-      <c r="Q13" t="str">
-        <v>https://1fichier.com/?cyay7uy9fg</v>
-      </c>
-      <c r="R13" t="str">
-        <v>https://1fichier.com/?63fp2qyu2i</v>
-      </c>
-      <c r="S13" t="str">
-        <v>https://1fichier.com/?uw5hg79haiu0mej1c6zb&amp;af=62851</v>
-      </c>
-      <c r="T13" t="str">
-        <v>https://1fichier.com/?vwk35hkul6t8x3dunx88&amp;af=62851</v>
-      </c>
-      <c r="U13" t="str">
-        <v>https://1fichier.com/?4jii58rk43nmw14okuhe</v>
-      </c>
-      <c r="V13" t="str">
-        <v>https://1fichier.com/?6pmmogos9d44dytu2ldd</v>
-      </c>
-      <c r="AD13" t="str">
-        <v>https://megaup.net/1vu2d/TLOZTWW_ziperto.com.part1.rar</v>
-      </c>
-      <c r="AE13" t="str">
-        <v>https://megaup.net/Pwzl/TLOZTWW_ziperto.com.part2.rar</v>
-      </c>
-      <c r="AH13" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AI13" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AJ13" t="str">
         <v>https://send.now/p0kynvesvb8g</v>
       </c>
-      <c r="AK13" t="str">
+      <c r="L13" t="str">
         <v>https://send.now/iah7d2ygo3v7</v>
       </c>
-      <c r="AL13" t="str">
+      <c r="M13" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1140,27 +990,30 @@
         <v>imagenes/WII U/Tekken Tag Tournament 2 Wii U Edition.jpg</v>
       </c>
       <c r="E14" t="str">
-        <v>No</v>
-      </c>
-      <c r="P14" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F14" t="str">
+        <v>No</v>
+      </c>
+      <c r="H14" t="str">
         <v>https://1fichier.com/?6tc8dcbjlwz1f93wgha5</v>
       </c>
-      <c r="AH14" t="str">
+      <c r="I14" t="str">
         <v>https://www.filecrypt.cc/Container/BE3F735C6B.html</v>
       </c>
-      <c r="AI14" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AJ14" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AK14" t="str">
+      <c r="J14" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="K14" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="L14" t="str">
         <v>https://www.filecrypt.cc/Container/8B18479874.html: https://www.filecrypt.cc/Container/8B18479874.html</v>
       </c>
-      <c r="AL14" t="str">
+      <c r="M14" t="str">
         <v>https://www.filecrypt.cc/Container/A63F253FB1.html: https://www.filecrypt.cc/Container/A63F253FB1.html</v>
       </c>
-      <c r="AM14" t="str">
+      <c r="N14" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1178,25 +1031,28 @@
         <v>imagenes/WII U/Tank! Tank! Tank!.jpg</v>
       </c>
       <c r="E15" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F15" t="str">
+        <v>No</v>
+      </c>
+      <c r="G15" t="str">
         <v>https://mega.nz/#!9LASyIgQ!8uhnu1IdQYTmS-2ELnh_N-s833H8hY0I2i0GTSyG4HE</v>
       </c>
-      <c r="P15" t="str">
+      <c r="H15" t="str">
         <v>https://1fichier.com/?eu5e6efuk5&amp;af=62851</v>
       </c>
-      <c r="W15" t="str">
+      <c r="I15" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J15" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K15" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T15" t="str">
         <v>https://drive.google.com/file/d/0B0lnKSdJsB3dRHRfTDR3dVQtV28/view</v>
-      </c>
-      <c r="AH15" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AI15" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AJ15" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
     <row r="16">
@@ -1213,30 +1069,18 @@
         <v>imagenes/WII U/Taiko no Tatsujin Atsumete Tomodachi Daisakusen.jpg</v>
       </c>
       <c r="E16" t="str">
-        <v>No</v>
-      </c>
-      <c r="Q16" t="str">
-        <v>https://1fichier.com/?r5ogmkufb1htp1lu27td</v>
-      </c>
-      <c r="R16" t="str">
-        <v>https://1fichier.com/?9n9ddxe9ilv9q58efz98</v>
-      </c>
-      <c r="S16" t="str">
-        <v>https://1fichier.com/?63o2sj4suvca8v27tdme</v>
-      </c>
-      <c r="X16" t="str">
-        <v>https://drive.google.com/file/d/1u6tYRvCGpoX1iV_GEMS4Ci8-XjCaPCY2/view?usp=sharing: https://drive.google.com/file/d/1u6tYRvCGpoX1iV_GEMS4Ci8-XjCaPCY2/view?usp=sharing</v>
-      </c>
-      <c r="Y16" t="str">
-        <v>https://nswgame.com/guide-fix-error-limit-download-google-drive/: https://nswgame.com/guide-fix-error-limit-download-google-drive/</v>
-      </c>
-      <c r="AH16" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AI16" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AJ16" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F16" t="str">
+        <v>No</v>
+      </c>
+      <c r="I16" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J16" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K16" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1254,27 +1098,24 @@
         <v>imagenes/WII U/Super Smash Bros for Wii U.jpg</v>
       </c>
       <c r="E17" t="str">
-        <v>No</v>
-      </c>
-      <c r="X17" t="str">
-        <v>https://drive.google.com/folderview?id=0B-b_aHxMLFVGcEtYMkxucEMwQkE&amp;usp=sharing</v>
-      </c>
-      <c r="Y17" t="str">
-        <v>https://nswgame.com/guide-fix-error-limit-download-google-drive/: https://nswgame.com/guide-fix-error-limit-download-google-drive/</v>
-      </c>
-      <c r="AH17" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F17" t="str">
+        <v>No</v>
+      </c>
+      <c r="I17" t="str">
         <v>https://www.filecrypt.cc/Container/B9E832912A.html</v>
       </c>
-      <c r="AI17" t="str">
+      <c r="J17" t="str">
         <v>https://www.filecrypt.cc/Container/E1AAA6A0F8.html</v>
       </c>
-      <c r="AJ17" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AK17" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AL17" t="str">
+      <c r="K17" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="L17" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="M17" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1292,27 +1133,18 @@
         <v>imagenes/WII U/Super Mario Maker.jpg</v>
       </c>
       <c r="E18" t="str">
-        <v>No</v>
-      </c>
-      <c r="Q18" t="str">
-        <v>https://1fichier.com/?x32hr247qruht6zg835z</v>
-      </c>
-      <c r="R18" t="str">
-        <v>https://1fichier.com/?qv5tmft5j7lqfa3kxe3m</v>
-      </c>
-      <c r="AD18" t="str">
-        <v>https://megaup.net/1tm8r/SMM-USA-LOADIINE-ZIPERTO.rar</v>
-      </c>
-      <c r="AE18" t="str">
-        <v>https://megaup.net/Noz6/SMM-USA-LOADIINE-UPDATE-ZIPERTO.rar</v>
-      </c>
-      <c r="AH18" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AI18" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AJ18" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F18" t="str">
+        <v>No</v>
+      </c>
+      <c r="I18" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J18" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K18" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1330,49 +1162,28 @@
         <v>imagenes/WII U/Super Mario 3D World.jpg</v>
       </c>
       <c r="E19" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F19" t="str">
         <v>Sí</v>
       </c>
-      <c r="F19" t="str">
+      <c r="G19" t="str">
         <v>https://x.com/intent/post?text=upload%20to%20mega.nz%20or%20reupload%20google%20drive%20please?&amp;url=https%3A%2F%2Fnswgame.com%2Fsuper-mario-3d-world%25ef%25bb%25bf-wii-u-download-free%2F%23comment-15000</v>
       </c>
-      <c r="Q19" t="str">
-        <v>https://1fichier.com/?4rgoujh6f5hircddlxk0&amp;af=62851</v>
-      </c>
-      <c r="R19" t="str">
-        <v>https://1fichier.com/?jrsj91kamn64pnba0gm4&amp;af=62851</v>
-      </c>
-      <c r="S19" t="str">
-        <v>https://1fichier.com/?xw3pts63cx</v>
+      <c r="I19" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J19" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K19" t="str">
+        <v>https://docs.google.com/uc?id=0B0lnKSdJsB3deXRpU3pJdGNMa0E&amp;export=download</v>
+      </c>
+      <c r="L19" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
       </c>
       <c r="T19" t="str">
-        <v>https://1fichier.com/?oy47ck7csl</v>
-      </c>
-      <c r="W19" t="str">
         <v>https://nswgame.com/guide-fix-error-limit-download-google-drive/: https://nswgame.com/guide-fix-error-limit-download-google-drive/</v>
-      </c>
-      <c r="AD19" t="str">
-        <v>https://megaup.net/2Yubx/SM-3DW-USA-LOADIINE-ZIPERTO.part1.rar</v>
-      </c>
-      <c r="AE19" t="str">
-        <v>https://megaup.net/1Czh9/SM-3DW-USA-LOADIINE-ZIPERTO.part2.rar</v>
-      </c>
-      <c r="AF19" t="str">
-        <v>https://megaup.net/1Czf3/SM3DW_ziperto.com.part1.rar</v>
-      </c>
-      <c r="AG19" t="str">
-        <v>https://megaup.net/1Czfv/SM3DW_ziperto.com.part2.rar</v>
-      </c>
-      <c r="AH19" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AI19" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AJ19" t="str">
-        <v>https://docs.google.com/uc?id=0B0lnKSdJsB3deXRpU3pJdGNMa0E&amp;export=download</v>
-      </c>
-      <c r="AK19" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
     <row r="20">
@@ -1389,21 +1200,24 @@
         <v>imagenes/WII U/Star Fox Zero.jpg</v>
       </c>
       <c r="E20" t="str">
-        <v>No</v>
-      </c>
-      <c r="AH20" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F20" t="str">
+        <v>No</v>
+      </c>
+      <c r="I20" t="str">
         <v>https://www.filecrypt.cc/Container/19670A6877.html</v>
       </c>
-      <c r="AI20" t="str">
+      <c r="J20" t="str">
         <v>https://www.filecrypt.cc/Container/EC5553E4F3.html</v>
       </c>
-      <c r="AJ20" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AK20" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AL20" t="str">
+      <c r="K20" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="L20" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="M20" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1421,33 +1235,24 @@
         <v>imagenes/WII U/Star Fox Guard.jpg</v>
       </c>
       <c r="E21" t="str">
-        <v>No</v>
-      </c>
-      <c r="G21" t="str">
-        <v>https://mega.nz/file/HqoxWBIT#cKiWYmBrF1CAW_TeOajwZ272FiNmp3FgvvxnXhqSoVc</v>
-      </c>
-      <c r="H21" t="str">
-        <v>https://mega.nz/file/u3QW3AZJ#MNWZoGgxxMeYWa71eGDFtXdIAbBuqbVx81_H-2f1BBw</v>
-      </c>
-      <c r="Q21" t="str">
-        <v>https://1fichier.com/?1j60sx9lpzlengri05f4&amp;af=1951572</v>
-      </c>
-      <c r="R21" t="str">
-        <v>https://1fichier.com/?k96ka5two8so6kjnr5rd&amp;af=1951572</v>
-      </c>
-      <c r="AH21" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F21" t="str">
+        <v>No</v>
+      </c>
+      <c r="I21" t="str">
         <v>https://send.cm/1nlx52fjr2ij</v>
       </c>
-      <c r="AI21" t="str">
+      <c r="J21" t="str">
         <v>https://send.cm/nlejg5k2nzin</v>
       </c>
-      <c r="AJ21" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AK21" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AL21" t="str">
+      <c r="K21" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="L21" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="M21" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1465,18 +1270,21 @@
         <v>imagenes/WII U/Tom Clancys Splinter Cell Blacklist.jpg</v>
       </c>
       <c r="E22" t="str">
-        <v>No</v>
-      </c>
-      <c r="P22" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F22" t="str">
+        <v>No</v>
+      </c>
+      <c r="H22" t="str">
         <v>https://1fichier.com/?i828opl9eig1wiqwlum9</v>
       </c>
-      <c r="AH22" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AI22" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AJ22" t="str">
+      <c r="I22" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J22" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K22" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1494,31 +1302,22 @@
         <v>imagenes/WII U/Spla﻿toon.jpg</v>
       </c>
       <c r="E23" t="str">
-        <v>No</v>
-      </c>
-      <c r="G23" t="str">
-        <v>https://mega.nz/file/OKoVRaIY#ck89OB1hREbwaEE5DzESdwA9CskB4AWEfK-V614zdSQ</v>
-      </c>
-      <c r="H23" t="str">
-        <v>https://mega.nz/file/ohQGAbAB#e-Jcvn5-ZZQcfmzsjc8oHVa74zYMeLpoUIRTjfuZYnY</v>
-      </c>
-      <c r="Q23" t="str">
-        <v>https://1fichier.com/?7e5cl33l8l&amp;af=62851</v>
-      </c>
-      <c r="R23" t="str">
-        <v>https://1fichier.com/?2ketoendew3hm2ut7pfh&amp;af=62851</v>
-      </c>
-      <c r="W23" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F23" t="str">
+        <v>No</v>
+      </c>
+      <c r="I23" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J23" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K23" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T23" t="str">
         <v>https://drive.google.com/file/d/0B0lnKSdJsB3dVDdNdjhfbkRqMTQ/view</v>
-      </c>
-      <c r="AH23" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AI23" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AJ23" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
     <row r="24">
@@ -1535,21 +1334,24 @@
         <v>imagenes/WII U/Sonic Lost World.jpg</v>
       </c>
       <c r="E24" t="str">
-        <v>No</v>
-      </c>
-      <c r="AH24" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F24" t="str">
+        <v>No</v>
+      </c>
+      <c r="I24" t="str">
         <v>https://www.filecrypt.cc/Container/26B1D3B971.html</v>
       </c>
-      <c r="AI24" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AJ24" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AK24" t="str">
+      <c r="J24" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="K24" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="L24" t="str">
         <v>https://filecrypt.cc/Container/48F95A7730.html</v>
       </c>
-      <c r="AL24" t="str">
+      <c r="M24" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1567,31 +1369,22 @@
         <v>imagenes/WII U/Sniper Elite V2.jpg</v>
       </c>
       <c r="E25" t="str">
-        <v>No</v>
-      </c>
-      <c r="G25" t="str">
-        <v>https://mega.nz/file/YRRVXIwJ#-dY_e49Hlt2vfG36tBzUehnOjxPmY__jCZkcW_0ywVo</v>
-      </c>
-      <c r="H25" t="str">
-        <v>https://x.com/intent/post?text=hey,%20guy%20look%20what%20I%20founddddddddddddd:https://mega.nz/file/YRRVX...%20&amp;url=https%3A%2F%2Fnswgame.com%2Fsniper-elite-v2-wii-u-download-free%2F%23comment-4851</v>
-      </c>
-      <c r="Q25" t="str">
-        <v>https://1fichier.com/?avel3pyepppjkxvl11f8</v>
-      </c>
-      <c r="R25" t="str">
-        <v>https://1fichier.com/?mxglbnt4tlqvblzvhmgl</v>
-      </c>
-      <c r="W25" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F25" t="str">
+        <v>No</v>
+      </c>
+      <c r="I25" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J25" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K25" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T25" t="str">
         <v>https://drive.google.com/file/d/1iogYKn9XXtHjMIrc7luygL7q-oRJtICk/view</v>
-      </c>
-      <c r="AH25" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AI25" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AJ25" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
     <row r="26">
@@ -1608,21 +1401,24 @@
         <v>imagenes/WII U/Shovel Knight.jpg</v>
       </c>
       <c r="E26" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F26" t="str">
+        <v>No</v>
+      </c>
+      <c r="G26" t="str">
         <v>https://mega.nz/#!rCxhiR4C!WMpZLNjdyaq5s58NUS2CTTCdxAh8yvmdohPue7GBpMo</v>
       </c>
-      <c r="P26" t="str">
+      <c r="H26" t="str">
         <v>https://1fichier.com/?bsa5yxqzq7&amp;af=62851</v>
       </c>
-      <c r="AH26" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AI26" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AJ26" t="str">
+      <c r="I26" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J26" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K26" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1640,18 +1436,21 @@
         <v>imagenes/WII U/Scribblenauts Unmasked a DC Comics Adventure.jpg</v>
       </c>
       <c r="E27" t="str">
-        <v>No</v>
-      </c>
-      <c r="P27" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F27" t="str">
+        <v>No</v>
+      </c>
+      <c r="H27" t="str">
         <v>https://1fichier.com/?0wtfkescp6higttwfajb&amp;af=62851</v>
       </c>
-      <c r="AH27" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AI27" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AJ27" t="str">
+      <c r="I27" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J27" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K27" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1669,18 +1468,21 @@
         <v>imagenes/WII U/S﻿cribblenauts Unlimited.jpg</v>
       </c>
       <c r="E28" t="str">
-        <v>No</v>
-      </c>
-      <c r="P28" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F28" t="str">
+        <v>No</v>
+      </c>
+      <c r="H28" t="str">
         <v>https://1fichier.com/?3casxdjztpntqds5i6on</v>
       </c>
-      <c r="AH28" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AI28" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AJ28" t="str">
+      <c r="I28" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J28" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K28" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1698,18 +1500,21 @@
         <v>imagenes/WII U/Resident Evil Revelations.jpg</v>
       </c>
       <c r="E29" t="str">
-        <v>No</v>
-      </c>
-      <c r="P29" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F29" t="str">
+        <v>No</v>
+      </c>
+      <c r="H29" t="str">
         <v>https://1fichier.com/?gxwwx5fh6ihkgc7ss433</v>
       </c>
-      <c r="AH29" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AI29" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AJ29" t="str">
+      <c r="I29" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J29" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K29" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1727,33 +1532,24 @@
         <v>imagenes/WII U/Rayman Legends.jpg</v>
       </c>
       <c r="E30" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F30" t="str">
         <v>Sí</v>
       </c>
-      <c r="Q30" t="str">
-        <v>https://1fichier.com/?gr74ra4yigd9yo9fyan2&amp;af=62851</v>
-      </c>
-      <c r="R30" t="str">
-        <v>https://1fichier.com/?xvcsk3t5tktw4cc509mc&amp;af=62851</v>
-      </c>
-      <c r="S30" t="str">
-        <v>https://x.com/intent/post?text=https://1fichier.com/?ncuswhkn20s3sgbtmins%20it%E2%80%99s%20alive%20^^&amp;url=https%3A%2F%2Fnswgame.com%2Frayman-legends-wii-u-download-free%2F%23comment-7688</v>
-      </c>
-      <c r="T30" t="str">
-        <v>https://1fichier.com/?ncuswhkn20s3sgbtmins: https://1fichier.com/?ncuswhkn20s3sgbtmins</v>
-      </c>
-      <c r="AH30" t="str">
+      <c r="I30" t="str">
         <v>https://send.now/d/F02y</v>
       </c>
-      <c r="AI30" t="str">
+      <c r="J30" t="str">
         <v>https://send.now/d/F07Y</v>
       </c>
-      <c r="AJ30" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AK30" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AL30" t="str">
+      <c r="K30" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="L30" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="M30" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1771,22 +1567,25 @@
         <v>imagenes/WII U/Project Zero Maiden of Black Water.jpg</v>
       </c>
       <c r="E31" t="str">
-        <v>No</v>
-      </c>
-      <c r="M31" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F31" t="str">
+        <v>No</v>
+      </c>
+      <c r="I31" t="str">
+        <v>https://www.filecrypt.cc/Container/DA9BEABAA1.html</v>
+      </c>
+      <c r="J31" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="K31" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="L31" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="P31" t="str">
         <v>http://www.mediafire.com/file/10cfma3ilqp0mx3/Meta_for_Project_Zero_-_Maiden_Of_Black_Water.zip: http://www.mediafire.com/file/10cfma3ilqp0mx3/Meta_for_Project_Zero_-_Maiden_Of_Black_Water.zip</v>
-      </c>
-      <c r="AH31" t="str">
-        <v>https://www.filecrypt.cc/Container/DA9BEABAA1.html</v>
-      </c>
-      <c r="AI31" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AJ31" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AK31" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
     <row r="32">
@@ -1803,48 +1602,27 @@
         <v>imagenes/WII U/Pokken Tournament.jpg</v>
       </c>
       <c r="E32" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F32" t="str">
         <v>Sí</v>
       </c>
-      <c r="Q32" t="str">
-        <v>https://x.com/intent/post?text=Retail%20NUS:https://1fichier.com/?tsnzfw7bbemt67rjpl55https://1...%20&amp;url=https%3A%2F%2Fnswgame.com%2Fpokken-tournament-wii-u-download-free%2F%23comment-8722</v>
-      </c>
-      <c r="R32" t="str">
-        <v>https://1fichier.com/?tsnzfw7bbemt67rjpl55: https://1fichier.com/?tsnzfw7bbemt67rjpl55</v>
-      </c>
-      <c r="S32" t="str">
-        <v>https://1fichier.com/?p8ua960otbo6wnr7ucgr: https://1fichier.com/?p8ua960otbo6wnr7ucgr</v>
-      </c>
-      <c r="T32" t="str">
-        <v>https://1fichier.com/?02zhn0d3hy4h7pzwue6p: https://1fichier.com/?02zhn0d3hy4h7pzwue6p</v>
-      </c>
-      <c r="U32" t="str">
-        <v>https://1fichier.com/?2efofq2pcm8aw9kkzw1n: https://1fichier.com/?2efofq2pcm8aw9kkzw1n</v>
-      </c>
-      <c r="X32" t="str">
-        <v>https://x.com/intent/post?text=also%20google%20drive%20link%20part%201:%20https://drive.google.com/file/d/1...%20&amp;url=https%3A%2F%2Fnswgame.com%2Fpokken-tournament-wii-u-download-free%2F%23comment-9786</v>
-      </c>
-      <c r="Y32" t="str">
-        <v>https://drive.google.com/file/d/18wbbHT7zh34zvcCYhCY8IARcZH5HjX6H/view: https://drive.google.com/file/d/18wbbHT7zh34zvcCYhCY8IARcZH5HjX6H/view</v>
-      </c>
-      <c r="Z32" t="str">
-        <v>https://nswgame.com/guide-fix-error-limit-download-google-drive/: https://nswgame.com/guide-fix-error-limit-download-google-drive/</v>
-      </c>
-      <c r="AH32" t="str">
+      <c r="I32" t="str">
         <v>https://filecrypt.co/Container/07974F0554.html</v>
       </c>
-      <c r="AI32" t="str">
+      <c r="J32" t="str">
         <v>https://www.filecrypt.cc/Container/30F6D7BDCB.html</v>
       </c>
-      <c r="AJ32" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AK32" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AL32" t="str">
+      <c r="K32" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="L32" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="M32" t="str">
         <v>https://filecrypt.cc/Container/30F6D7BDCB.html: https://filecrypt.cc/Container/30F6D7BDCB.html</v>
       </c>
-      <c r="AM32" t="str">
+      <c r="N32" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1862,18 +1640,21 @@
         <v>imagenes/WII U/Pikmin 3.jpg</v>
       </c>
       <c r="E33" t="str">
-        <v>No</v>
-      </c>
-      <c r="AH33" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F33" t="str">
+        <v>No</v>
+      </c>
+      <c r="I33" t="str">
         <v>https://www.filecrypt.cc/Container/60EBECEB44.html</v>
       </c>
-      <c r="AI33" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AJ33" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AK33" t="str">
+      <c r="J33" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="K33" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="L33" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1891,21 +1672,24 @@
         <v>imagenes/WII U/One Piece Unlimited World Red.jpg</v>
       </c>
       <c r="E34" t="str">
-        <v>No</v>
-      </c>
-      <c r="P34" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F34" t="str">
+        <v>No</v>
+      </c>
+      <c r="H34" t="str">
         <v>https://1fichier.com/?18z8t12xpwif4dduc3d8</v>
       </c>
-      <c r="AH34" t="str">
+      <c r="I34" t="str">
         <v>https://www.filecrypt.cc/Container/8281CEEBFA.html</v>
       </c>
-      <c r="AI34" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AJ34" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AK34" t="str">
+      <c r="J34" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="K34" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="L34" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1923,43 +1707,28 @@
         <v>imagenes/WII U/Nintendo Land.jpg</v>
       </c>
       <c r="E35" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F35" t="str">
         <v>Sí</v>
       </c>
-      <c r="G35" t="str">
-        <v>https://mega.nz/file/6dIH2SzT#chVzGWF15CkevBw7XyyI7xV1llZ3__oeDWBOZ363Gk8</v>
-      </c>
-      <c r="H35" t="str">
-        <v>https://mega.nz/file/eMYkgAAL#BwnAhl093jF3k783O5dnPCEVwMc-oc12IiVzPD5deTc</v>
-      </c>
       <c r="I35" t="str">
-        <v>https://mega.nz/file/rNRWVS6Y#AuvD9zktB-UeDRzPGoaZo2kyjfR097-Xa_WUIC3Hd40</v>
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J35" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K35" t="str">
+        <v>https://filecrypt.cc/Container/B40C42C657.html</v>
+      </c>
+      <c r="L35" t="str">
+        <v>https://nswgame.com/running-fable-petite-party-nintendo-switch-nsp-xci-nsz-download-free/</v>
       </c>
       <c r="M35" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="P35" t="str">
         <v>https://www.mediafire.com/file/z9clkqvfd05yvn1/NL-USA-LOADIINE-UPDATE-ZIPERTO.rar/file</v>
-      </c>
-      <c r="Q35" t="str">
-        <v>https://1fichier.com/?hjrse0z5sv0gii0t31y5</v>
-      </c>
-      <c r="R35" t="str">
-        <v>https://1fichier.com/?prm5nq25d149nqz3an3c</v>
-      </c>
-      <c r="S35" t="str">
-        <v>https://1fichier.com/?nfxk1552nmzazjf41lox</v>
-      </c>
-      <c r="AH35" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AI35" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AJ35" t="str">
-        <v>https://filecrypt.cc/Container/B40C42C657.html</v>
-      </c>
-      <c r="AK35" t="str">
-        <v>https://nswgame.com/running-fable-petite-party-nintendo-switch-nsp-xci-nsz-download-free/</v>
-      </c>
-      <c r="AL35" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
     <row r="36">
@@ -1976,46 +1745,22 @@
         <v>imagenes/WII U/New Super Mario Bros U.jpg</v>
       </c>
       <c r="E36" t="str">
-        <v>No</v>
-      </c>
-      <c r="Q36" t="str">
-        <v>https://1fichier.com/?tr6kcuy9cje8kd8z8ffh</v>
-      </c>
-      <c r="R36" t="str">
-        <v>https://1fichier.com/?xut41cnxko9oqs1s1aoo</v>
-      </c>
-      <c r="S36" t="str">
-        <v>https://1fichier.com/?ladmc7l12put387fiktj</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F36" t="str">
+        <v>No</v>
+      </c>
+      <c r="I36" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J36" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K36" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
       </c>
       <c r="T36" t="str">
-        <v>https://1fichier.com/?merj4ylqft010bd2oiht</v>
-      </c>
-      <c r="U36" t="str">
-        <v>https://1fichier.com/?voqoljigq6r0tizr0rx5</v>
-      </c>
-      <c r="W36" t="str">
         <v>https://nswgame.com/guide-fix-error-limit-download-google-drive/: https://nswgame.com/guide-fix-error-limit-download-google-drive/</v>
-      </c>
-      <c r="AD36" t="str">
-        <v>https://megaup.net/R0fc/NSMB-U-USA-LOADIINE-ZIPERTO.rar</v>
-      </c>
-      <c r="AE36" t="str">
-        <v>https://megaup.net/R0eq/NSMB-U-USA-LOADIINE-UPDATE-ZIPERTO.rar</v>
-      </c>
-      <c r="AF36" t="str">
-        <v>https://megaup.net/R0eh/NSMB-U-USA-LOADIINE-DLC-ZIPERTO.rar</v>
-      </c>
-      <c r="AG36" t="str">
-        <v>https://megaup.net/9n90/Fix-New_Super_Mario_Bros_U-Ziperto.rar</v>
-      </c>
-      <c r="AH36" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AI36" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AJ36" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
     <row r="37">
@@ -2032,25 +1777,28 @@
         <v>imagenes/WII U/New Super Luigi U.jpg</v>
       </c>
       <c r="E37" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F37" t="str">
+        <v>No</v>
+      </c>
+      <c r="G37" t="str">
         <v>https://mega.nz/file/AFgj3KiA#Hw5nBTpnslvy5V60pc3KnntAHgI9hCQZylOSQqHQcs8</v>
       </c>
-      <c r="P37" t="str">
+      <c r="H37" t="str">
         <v>https://1fichier.com/?hfq7veghjtl16s0pdae5</v>
       </c>
-      <c r="AC37" t="str">
+      <c r="I37" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J37" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K37" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="O37" t="str">
         <v>https://megaup.net/R0gs/NSL-U-USA-LOADIINE-ZIPERTO.rar</v>
-      </c>
-      <c r="AH37" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AI37" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AJ37" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
     <row r="38">
@@ -2067,18 +1815,21 @@
         <v>imagenes/WII U/Need for Speed Most Wanted U.jpg</v>
       </c>
       <c r="E38" t="str">
-        <v>No</v>
-      </c>
-      <c r="AH38" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F38" t="str">
+        <v>No</v>
+      </c>
+      <c r="I38" t="str">
         <v>https://www.filecrypt.cc/Container/09B2D00DA1.html</v>
       </c>
-      <c r="AI38" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AJ38" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AK38" t="str">
+      <c r="J38" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="K38" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="L38" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -2096,24 +1847,27 @@
         <v>imagenes/WII U/N﻿inja Gaiden 3 Razors Edge.jpg</v>
       </c>
       <c r="E39" t="str">
-        <v>No</v>
-      </c>
-      <c r="AH39" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F39" t="str">
+        <v>No</v>
+      </c>
+      <c r="I39" t="str">
         <v>https://www.filecrypt.cc/Container/69732C24EE.html</v>
       </c>
-      <c r="AI39" t="str">
+      <c r="J39" t="str">
         <v>https://www.filecrypt.cc/Container/3E26B634FF.html</v>
       </c>
-      <c r="AJ39" t="str">
+      <c r="K39" t="str">
         <v>https://www.filecrypt.cc/Container/5C58735528.html</v>
       </c>
-      <c r="AK39" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AL39" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AM39" t="str">
+      <c r="L39" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="M39" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="N39" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -2131,27 +1885,21 @@
         <v>imagenes/WII U/Monster Hunter 3 Ultimate.jpg</v>
       </c>
       <c r="E40" t="str">
-        <v>No</v>
-      </c>
-      <c r="Q40" t="str">
-        <v>https://x.com/intent/post?text=https://1fichier.com/?ooaopvm1mw5he81krmfvhttps://1fic...%20&amp;url=https%3A%2F%2Fnswgame.com%2Fmonster-hunter-3-ultimate-wii-u-download-free%2F%23comment-36932</v>
-      </c>
-      <c r="R40" t="str">
-        <v>https://1fichier.com/?ooaopvm1mw5he81krmfv: https://1fichier.com/?ooaopvm1mw5he81krmfv</v>
-      </c>
-      <c r="S40" t="str">
-        <v>https://1fichier.com/?khzln0zfoj558akyndel: https://1fichier.com/?khzln0zfoj558akyndel</v>
-      </c>
-      <c r="AH40" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F40" t="str">
+        <v>No</v>
+      </c>
+      <c r="I40" t="str">
         <v>https://www.filecrypt.cc/Container/A498E1A222.html</v>
       </c>
-      <c r="AI40" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AJ40" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AK40" t="str">
+      <c r="J40" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="K40" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="L40" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -2169,27 +1917,1592 @@
         <v>imagenes/WII U/Minecraft Super Mario Edition.jpg</v>
       </c>
       <c r="E41" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F41" t="str">
+        <v>No</v>
+      </c>
+      <c r="G41" t="str">
         <v>https://mega.nz/#!EvRFGLYb!cQHvZ6xz4r1xEtbQx3Dt83d4rr0fuhMKkdMVmxWKLx8</v>
       </c>
-      <c r="P41" t="str">
+      <c r="H41" t="str">
         <v>https://1fichier.com/?npbi4kkq7r&amp;af=62851</v>
       </c>
-      <c r="AH41" t="str">
-        <v>https://nswgame.com/guide-download-game/</v>
-      </c>
-      <c r="AI41" t="str">
-        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
-      </c>
-      <c r="AJ41" t="str">
+      <c r="I41" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J41" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K41" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>FIFA 13</v>
+      </c>
+      <c r="B42" t="str">
+        <v>https://nswgame.com/fifa-13-wii-u-download-free/</v>
+      </c>
+      <c r="C42" t="str">
+        <v>https://www.youtube.com/embed/KAaK3lUxPMU</v>
+      </c>
+      <c r="D42" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="E42" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F42" t="str">
+        <v>No</v>
+      </c>
+      <c r="H42" t="str">
+        <v>https://1fichier.com/?r2kwcjunv2q5ibw6sxy6</v>
+      </c>
+      <c r="I42" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J42" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K42" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T42" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="A43" t="str">
+        <v>Disney DuckTales Remastered</v>
+      </c>
+      <c r="B43" t="str">
+        <v>https://nswgame.com/disney-ducktales-remastered-wii-u-download-free/</v>
+      </c>
+      <c r="C43" t="str">
+        <v>https://www.youtube.com/embed/mr-5-BpxwSo</v>
+      </c>
+      <c r="D43" t="str">
+        <v>imagenes/WII U/Disney DuckTales Remastered.jpg</v>
+      </c>
+      <c r="E43" t="str" xml:space="preserve">
+        <v xml:space="preserve">Embark on an authentic DuckTales adventure, as Scrooge McDuck and his three nephews; Huey, Dewey and Louie travel to exotic locations throughout the world in their quest to retrieve the five Legendary Treasures.
+Go back to one of the golden ages of gaming, but now refined with a level of detail that will please the most devoted Disney or retro Capcom fan, alike. Featuring hand-drawn animated sprites, authentic Disney character voices talent and richly painted level backgrounds from the classic cartoon TV series, Scrooge McDuck and family come to life like never before. The gameplay retains the authenticity of its 8-bit predecessor, simple and fun, with slight modifications to improve gameplay flow and design.
+Hello, the link does not work. May we please have a new link?</v>
+      </c>
+      <c r="F43" t="str">
+        <v>No</v>
+      </c>
+      <c r="G43" t="str">
+        <v>https://mega.nz/file/YSZ0iK6R#GDEZTkPT9Zb9nmC-MthCOs8gCrocA8hM9RFJ-5V2dKg</v>
+      </c>
+      <c r="I43" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J43" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K43" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="U43" t="str">
+        <v>https://drive.google.com/file/d/1_GGlYf5vyMydZU1IkSlpRIY21dns4EZO/view</v>
+      </c>
+      <c r="V43" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Donkey Kong Country Tropical Freeze</v>
+      </c>
+      <c r="B44" t="str">
+        <v>https://nswgame.com/donkey-kong-country-tropical-freeze-wii-u-download-free/</v>
+      </c>
+      <c r="C44" t="str">
+        <v>https://www.youtube.com/embed/DueE8vJXpo8</v>
+      </c>
+      <c r="D44" t="str">
+        <v>imagenes/WII U/Donkey Kong Country Tropical Freeze.jpg</v>
+      </c>
+      <c r="E44" t="str">
+        <v>game start as normaly…with cemu emulator… YOU ROCKS!</v>
+      </c>
+      <c r="F44" t="str">
+        <v>No</v>
+      </c>
+      <c r="I44" t="str">
+        <v>https://www.filecrypt.cc/Container/3D95D24C2F.html</v>
+      </c>
+      <c r="J44" t="str">
+        <v>https://www.filecrypt.cc/Container/AA318BAED8.html</v>
+      </c>
+      <c r="K44" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="L44" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="M44" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T44" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+    </row>
+    <row r="45" xml:space="preserve">
+      <c r="A45" t="str">
+        <v>Devils Third</v>
+      </c>
+      <c r="B45" t="str">
+        <v>https://nswgame.com/devils-third%ef%bb%bf-wii-u-download-free/</v>
+      </c>
+      <c r="C45" t="str">
+        <v>https://www.youtube.com/embed/7yTldFe2m-A</v>
+      </c>
+      <c r="D45" t="str">
+        <v>imagenes/WII U/Devils Third.jpg</v>
+      </c>
+      <c r="E45" t="str" xml:space="preserve">
+        <v xml:space="preserve">From the creative mind of legendary designer Tomonobu Itagaki comes Devil’s Third, an over-the-top, third-person action shooter that combines modern military weaponry with ninja-style swordplay and melee combat. It has a unique vision for a deep and challenging online mode that blends clan-based action, resource management and strategy.
+At the heart of the single-player campaign is Ivan, a former mercenary let loose from his incarceration to right the wrongs of his past and take down a shadowy terrorist group he once belonged to. With the worlds satellites and electrical weaponry having been wiped out, and warfare once again reduced to close combat between soldiers, Ivan must use a colourful array of weaponry to shoot and attack his way through any foe standing in the way of his attempt at redemption. With fast-paced combat and finishing moves galore, a day in the life of Ivan is anything but ordinary
+The games online multiplayer mode, meanwhile, offers up a grim future whereby the terrorists have won, and chaos reigns supreme. As an ordinary citizen, you can join a clan and help reclaim the United States by forming allegiances with other factions, or go all-out as a mercenary and endlessly assault other players bases, opting for anarchy over clan diplomacy! But at the heart of the online play is the ability to customise your base alongside other members of your clan, with successful battling resulting in rewards that can be used to improve your defences. With constant assaults from other clans, youll have to be on your toes to defend your territory.</v>
+      </c>
+      <c r="F45" t="str">
+        <v>No</v>
+      </c>
+      <c r="I45" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T45" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Darksiders 2</v>
+      </c>
+      <c r="B46" t="str">
+        <v>https://nswgame.com/darksiders-2%ef%bb%bf%ef%bb%bf-wii-u-download-free/</v>
+      </c>
+      <c r="C46" t="str">
+        <v>https://www.youtube.com/embed/N3TpRIlpGKQ</v>
+      </c>
+      <c r="D46" t="str">
+        <v>imagenes/WII U/Darksiders 2.jpg</v>
+      </c>
+      <c r="E46" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F46" t="str">
+        <v>No</v>
+      </c>
+      <c r="I46" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J46" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K46" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T46" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+      <c r="W46" t="str">
+        <v>https://1fichier.com/?1zh4cn51o4f7sh71j38l</v>
+      </c>
+      <c r="X46" t="str">
+        <v>https://x.com/intent/post?text=https://1fichier.com/?1zh4cn51o4f7sh71j38l%20try%20thi...%20&amp;url=https%3A%2F%2Fnswgame.com%2Fdarksiders-2%25ef%25bb%25bf%25ef%25bb%25bf-wii-u-download-free%2F%23comment-16374</v>
+      </c>
+    </row>
+    <row r="47" xml:space="preserve">
+      <c r="A47" t="str">
+        <v>Captain Toad Treasure Tracker</v>
+      </c>
+      <c r="B47" t="str">
+        <v>https://nswgame.com/captain-toad-treasure-tracker-wii-u-download-free/</v>
+      </c>
+      <c r="C47" t="str">
+        <v>https://www.youtube.com/embed/32nV2PKIv5Y</v>
+      </c>
+      <c r="D47" t="str">
+        <v>imagenes/WII U/Captain Toad Treasure Tracker.jpg</v>
+      </c>
+      <c r="E47" t="str" xml:space="preserve">
+        <v xml:space="preserve">Could you please upload anywhere but 1Fich? Thank you
+Added new Send link for base game, new Megaup link for update.
+just the base game, but we uploaded some new links, check them ^^</v>
+      </c>
+      <c r="F47" t="str">
+        <v>No</v>
+      </c>
+      <c r="I47" t="str">
+        <v>https://send.now/d/NaVB</v>
+      </c>
+      <c r="J47" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="K47" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="L47" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="O47" t="str">
+        <v>https://megaup.net/1Tbyf/CTTT-USA-LOADIINE-UPDATE-ZIPERTO.rar</v>
+      </c>
+      <c r="T47" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+      <c r="W47" t="str">
+        <v>https://1fichier.com/?2nr685gf0n0jzxbugn7t</v>
+      </c>
+      <c r="X47" t="str">
+        <v>https://1fichier.com/?gg6q5v26ia4jzfproi2z</v>
+      </c>
+    </row>
+    <row r="48" xml:space="preserve">
+      <c r="A48" t="str">
+        <v>Call of Duty Ghosts</v>
+      </c>
+      <c r="B48" t="str">
+        <v>https://nswgame.com/call-of-duty-ghosts-wii-u-download-free/</v>
+      </c>
+      <c r="C48" t="str">
+        <v>https://www.youtube.com/embed/8DVkMsCMdzI</v>
+      </c>
+      <c r="D48" t="str">
+        <v>imagenes/WII U/Call of Duty Ghosts.jpg</v>
+      </c>
+      <c r="E48" t="str" xml:space="preserve">
+        <v xml:space="preserve">plz help me ..how to make common.key title.key ..if anybody have the video plz show me how to make it…i realy want to play this …i try every thing i can ..but it dont work with wud2app …
+common key: easy
+title key: 28512A78013B127E418F02A1F45EFB99
+I tried the USA version on a Pal console. The game worked perfectly (without using spiik app to change region) which means that it’s region free game. As someone mentioned previously, it has only the wud file and you need game. Key and common. Key files to extract it from wud to support (this is done with wud2app program). Thank you for sharing.</v>
+      </c>
+      <c r="F48" t="str">
+        <v>No</v>
+      </c>
+      <c r="H48" t="str">
+        <v>https://1fichier.com/?v8krcb6esee5o6q9sr0a</v>
+      </c>
+      <c r="I48" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J48" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K48" t="str">
+        <v>https://anotepad.com/notes/n2mqx3ga</v>
+      </c>
+      <c r="L48" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T48" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+    </row>
+    <row r="49" xml:space="preserve">
+      <c r="A49" t="str">
+        <v>Call of Duty Black Ops 2</v>
+      </c>
+      <c r="B49" t="str">
+        <v>https://nswgame.com/call-of-duty-black-ops-2-wii-u-download-free/</v>
+      </c>
+      <c r="C49" t="str">
+        <v>https://www.youtube.com/embed/fYCv9WOM0-s</v>
+      </c>
+      <c r="D49" t="str">
+        <v>imagenes/WII U/Call of Duty Black Ops 2.jpg</v>
+      </c>
+      <c r="E49" t="str" xml:space="preserve">
+        <v xml:space="preserve">Would you tell me how to convert it ? please help
+im so confused with wud2app
+Hi
+I used JWUDTool that requires java, all I did is to paste the game in the same folder and run Powershell and write the commands
+the game is in Wud format, I used JWUDTool, it requires java, you run wether cmd or power shell in the folder (the game has to be in the same folder as this program), then write the commad</v>
+      </c>
+      <c r="F49" t="str">
+        <v>No</v>
+      </c>
+      <c r="I49" t="str">
+        <v>https://www.filecrypt.cc/Container/BE41900B52.html: https://www.filecrypt.cc/Container/BE41900B52.html</v>
+      </c>
+      <c r="J49" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T49" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+      <c r="W49" t="str">
+        <v>https://1fichier.com/?sq2pi20dqhb7yxweo1mr: https://1fichier.com/?sq2pi20dqhb7yxweo1mr</v>
+      </c>
+      <c r="X49" t="str">
+        <v>https://1fichier.com/?upwxa0d21cxviq4an41w: https://1fichier.com/?upwxa0d21cxviq4an41w</v>
+      </c>
+      <c r="Y49" t="str">
+        <v>https://1fichier.com/?tqfijucqvbjw28geepzz: https://1fichier.com/?tqfijucqvbjw28geepzz</v>
+      </c>
+      <c r="Z49" t="str">
+        <v>https://x.com/intent/post?text=hunter%20trophy%202%20europa:%20https://1fichier.com/?c306iduzudt...%20&amp;url=https%3A%2F%2Fnswgame.com%2Fcall-of-duty-black-ops-2-wii-u-download-free%2F%23comment-7662</v>
+      </c>
+      <c r="AA49" t="str">
+        <v>https://1fichier.com/?c306iduzudtexxh0nkuu: https://1fichier.com/?c306iduzudtexxh0nkuu</v>
+      </c>
+      <c r="AB49" t="str">
+        <v>https://x.com/intent/post?text=This%20one:%20https://1fichier.com/?vnczrcs0p1eriabl34t1%20?%20^^...%20&amp;url=https%3A%2F%2Fnswgame.com%2Fcall-of-duty-black-ops-2-wii-u-download-free%2F%23comment-7677</v>
+      </c>
+      <c r="AC49" t="str">
+        <v>https://1fichier.com/?vnczrcs0p1eriabl34t1: https://1fichier.com/?vnczrcs0p1eriabl34t1</v>
+      </c>
+    </row>
+    <row r="50" xml:space="preserve">
+      <c r="A50" t="str">
+        <v>Ben 10 Omniverse 2</v>
+      </c>
+      <c r="B50" t="str">
+        <v>https://nswgame.com/ben-10-omniverse-2-wii-u-download-free/</v>
+      </c>
+      <c r="C50" t="str">
+        <v>https://www.youtube.com/embed/S4mgMM5znfI</v>
+      </c>
+      <c r="D50" t="str">
+        <v>imagenes/WII U/Ben 10 Omniverse 2.jpg</v>
+      </c>
+      <c r="E50" t="str" xml:space="preserve">
+        <v xml:space="preserve">The Incursean battle begins! Multi-alien combos! 17 alien forms!
+Ben 10 Omniverse 2 has everything fans love about the hit series: Aliens, Action, and an all-new Adventure! The fastest Ben 10 game ever puts Ben in a race against the clock to make every alien transformation count in his battle against the all-new Incursean invaders.
+Set off on an all-new adventure with Ben as he infiltrates Incursean battleships to save the resistance fighters. Face off against new enemies featuring authentic voices in an all-new story written by the writers of the actual Ben 10 Omniverse TV series. All-new brawl sequences and fast paced alien switching action make this the most intense Ben 10 game yet!</v>
+      </c>
+      <c r="F50" t="str">
+        <v>No</v>
+      </c>
+      <c r="H50" t="str">
+        <v>https://1fichier.com/?a98llv2k0d2hi46vps8h</v>
+      </c>
+      <c r="I50" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J50" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K50" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T50" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+    </row>
+    <row r="51" xml:space="preserve">
+      <c r="A51" t="str">
+        <v>Bayonetta 2</v>
+      </c>
+      <c r="B51" t="str">
+        <v>https://nswgame.com/bayonetta-2-wii-u-download-free/</v>
+      </c>
+      <c r="C51" t="str">
+        <v>https://www.youtube.com/embed/OAPOhk4A7ps</v>
+      </c>
+      <c r="D51" t="str">
+        <v>imagenes/WII U/Bayonetta 2.jpg</v>
+      </c>
+      <c r="E51" t="str" xml:space="preserve">
+        <v xml:space="preserve">I checked and they’re alive, except for part 4 of megaup link.
+Check the new link we added, it’s almost 13gb, hope it includes dlc in there :((</v>
+      </c>
+      <c r="F51" t="str">
+        <v>No</v>
+      </c>
+      <c r="I51" t="str">
+        <v>https://filecrypt.co/Container/F66850BD36.html</v>
+      </c>
+      <c r="J51" t="str">
+        <v>https://www.filecrypt.cc/Container/8868F0DB9F.html</v>
+      </c>
+      <c r="K51" t="str">
+        <v>https://www.filecrypt.cc/Container/2A619C6DC3.html</v>
+      </c>
+      <c r="L51" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="M51" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="N51" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="U51" t="str">
+        <v>https://nswgame.com/guide-fix-error-limit-download-google-drive/: https://nswgame.com/guide-fix-error-limit-download-google-drive/</v>
+      </c>
+      <c r="V51" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+    </row>
+    <row r="52" xml:space="preserve">
+      <c r="A52" t="str">
+        <v>Bayonetta</v>
+      </c>
+      <c r="B52" t="str">
+        <v>https://nswgame.com/bayonetta-wii-u-download-free/</v>
+      </c>
+      <c r="C52" t="str">
+        <v>https://www.youtube.com/embed/7W0SDrkTRcs</v>
+      </c>
+      <c r="D52" t="str">
+        <v>imagenes/WII U/Bayonetta.jpg</v>
+      </c>
+      <c r="E52" t="str" xml:space="preserve">
+        <v xml:space="preserve">sorry but the link died again
+can you maybe fix it? please?</v>
+      </c>
+      <c r="F52" t="str">
+        <v>No</v>
+      </c>
+      <c r="I52" t="str">
+        <v>https://www.filecrypt.cc/Container/05841DC7D7.html</v>
+      </c>
+      <c r="J52" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="K52" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="L52" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T52" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+    </row>
+    <row r="53" xml:space="preserve">
+      <c r="A53" t="str">
+        <v>Batman Arkham Origins</v>
+      </c>
+      <c r="B53" t="str">
+        <v>https://nswgame.com/batman-arkham-origins-wii-u-download-free/</v>
+      </c>
+      <c r="C53" t="str">
+        <v>https://www.youtube.com/embed/gWHK5SPkn7w</v>
+      </c>
+      <c r="D53" t="str">
+        <v>imagenes/WII U/Batman Arkham Origins.jpg</v>
+      </c>
+      <c r="E53" t="str" xml:space="preserve">
+        <v xml:space="preserve">why does it say that the password is wrong?
+I have tried by typing it myself just as it is or by copy pasting, nothing works
+They’re dead links :(( Sorry but I don’t have this game anymore.
+thank you! very much appreciated, thanks for making the hardest gems to find available!</v>
+      </c>
+      <c r="F53" t="str">
+        <v>No</v>
+      </c>
+      <c r="I53" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T53" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+    </row>
+    <row r="54" xml:space="preserve">
+      <c r="A54" t="str">
+        <v>B﻿atman Arkham City Armore﻿d E﻿dition</v>
+      </c>
+      <c r="B54" t="str">
+        <v>https://nswgame.com/b%ef%bb%bfatman-arkham-city-armore%ef%bb%bfd-e%ef%bb%bfdition-wii-u-download-free/</v>
+      </c>
+      <c r="C54" t="str">
+        <v>https://www.youtube.com/embed/u6LMxYNiz_w</v>
+      </c>
+      <c r="D54" t="str">
+        <v>imagenes/WII U/B﻿atman Arkham City Armore﻿d E﻿dition.jpg</v>
+      </c>
+      <c r="E54" t="str" xml:space="preserve">
+        <v xml:space="preserve">I can’t find the amazing spider Man 2 for Wii u
+Or isn’t it available in this site?
+hello
+i was looking for wiiu game of watch dog and the walking dead survival instinct and i didn’t find them in this site…
+i can provide links
+It’s just that I mostly focus on nintendo switch games now :((</v>
+      </c>
+      <c r="F54" t="str">
+        <v>No</v>
+      </c>
+      <c r="H54" t="str">
+        <v>https://1fichier.com/?cc7rqxdpjdy7qq72covb</v>
+      </c>
+      <c r="I54" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J54" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K54" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T54" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Assassins Creed IV Black Flag</v>
+      </c>
+      <c r="B55" t="str">
+        <v>https://nswgame.com/assassins-creed-iv-black-flag-wii-u-download-free/</v>
+      </c>
+      <c r="C55" t="str">
+        <v>https://www.youtube.com/embed/Yf8kLqUfzCc</v>
+      </c>
+      <c r="D55" t="str">
+        <v>imagenes/WII U/Assassins Creed IV Black Flag.jpg</v>
+      </c>
+      <c r="E55" t="str">
+        <v>Game: Send (Part 1 – Part 2 – Part 3) – 1fichier (Part 1 – Part 2 – Part 3)</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Sí</v>
+      </c>
+      <c r="I55" t="str">
+        <v>https://send.now/d/8AMC</v>
+      </c>
+      <c r="J55" t="str">
+        <v>https://send.now/d/8APn</v>
+      </c>
+      <c r="K55" t="str">
+        <v>https://send.now/d/8AQW</v>
+      </c>
+      <c r="L55" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="M55" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="N55" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T55" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+      <c r="W55" t="str">
+        <v>https://1fichier.com/?fwrgojtd10&amp;af=62851</v>
+      </c>
+      <c r="X55" t="str">
+        <v>https://1fichier.com/?1a7or23obw&amp;af=62851</v>
+      </c>
+      <c r="Y55" t="str">
+        <v>https://1fichier.com/?q1l0hjqi33&amp;af=62851</v>
+      </c>
+    </row>
+    <row r="56" xml:space="preserve">
+      <c r="A56" t="str">
+        <v>Art Academy SketchPad</v>
+      </c>
+      <c r="B56" t="str">
+        <v>https://nswgame.com/art-academy-sketchpad-wii-u-download-free/</v>
+      </c>
+      <c r="C56" t="str">
+        <v>https://www.youtube.com/embed/NDErOuysAV8</v>
+      </c>
+      <c r="D56" t="str">
+        <v>imagenes/WII U/Art Academy SketchPad.jpg</v>
+      </c>
+      <c r="E56" t="str" xml:space="preserve">
+        <v xml:space="preserve">Art Academy: SketchPad is a robust art application that anyone can enjoy – from beginners to experts of all ages. Unleash your creativity using realistic stylus and touch screen-based controls. The tools at your disposal allow for an amazing level of detail. The huge variety of pencils, colored pencils, and pastels behave just like the real thing – with additional tools to further enhance your experience.
+Use a pre-loaded image as a subject, or anything else you wish to create works of art to your hearts content. When youre done, you can instantly share your creation by posting directly to Miiverse!
+So sorry we couldn’t find alternate links for this one :((</v>
+      </c>
+      <c r="F56" t="str">
+        <v>No</v>
+      </c>
+      <c r="I56" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Art Academy Atelier</v>
+      </c>
+      <c r="B57" t="str">
+        <v>https://nswgame.com/art-academy-atelier%ef%bb%bf-wii-u-download-free/</v>
+      </c>
+      <c r="C57" t="str">
+        <v>https://www.youtube.com/embed/hSeY9FFmnBc</v>
+      </c>
+      <c r="D57" t="str">
+        <v>imagenes/WII U/Art Academy Atelier.jpg</v>
+      </c>
+      <c r="E57" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F57" t="str">
+        <v>No</v>
+      </c>
+      <c r="H57" t="str">
+        <v>https://1fichier.com/?ywzf6zeny86qfomlazy1</v>
+      </c>
+      <c r="I57" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J57" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K57" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+    </row>
+    <row r="58" xml:space="preserve">
+      <c r="A58" t="str">
+        <v>Animal Crossing amiibo Festival</v>
+      </c>
+      <c r="B58" t="str">
+        <v>https://nswgame.com/animal-crossing-amiibo-festival-wii-u-download-free/</v>
+      </c>
+      <c r="C58" t="str">
+        <v>https://www.youtube.com/embed/-GIveAP_wtg</v>
+      </c>
+      <c r="D58" t="str">
+        <v>imagenes/WII U/Animal Crossing amiibo Festival.jpg</v>
+      </c>
+      <c r="E58" t="str" xml:space="preserve">
+        <v xml:space="preserve">The Animal Crossing: amiibo Festival game is a brand-new way to play with your favorite Animal Crossing characters. Your amiibo figures are front-and-center in this party game, and you’ll get to use them with fun content. Bring to life an expansive and dynamic board game where the board is based on the months of the year like the core Animal Crossing series. The goal? Make your villager the happiest in town and party hard with your friends.
+* Party with favorite Animal Crossing characters like Isabelle and Tom Nookwho have become amiibo.
+* Experience the Animal Crossing universe in light-hearted board games based on the calendar, including the four seasons and seasonal events.
+* Bring your amiibo to the party, collect Happy Points, play with your friends, and save your Happy Points to your amiibo to expand your own game even more.
+* Use Animal Crossing amiibo cards in fun minigames.</v>
+      </c>
+      <c r="F58" t="str">
+        <v>No</v>
+      </c>
+      <c r="G58" t="str">
+        <v>https://mega.nz/file/VRAXyCSb#YZW12Eqv99C_6dOnYBRX9ShTIVIMdXBghuqgVFW2qDQ</v>
+      </c>
+      <c r="H58" t="str">
+        <v>https://1fichier.com/?pia17fe26q3llk58njon&amp;af=62851</v>
+      </c>
+      <c r="I58" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J58" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K58" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="P58" t="str">
+        <v>http://www.mediafire.com/file/0kqw7tqtk5892we/ACAF_loadiine_ziperto.com.rar/file</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Angry Birds Trilogy</v>
+      </c>
+      <c r="B59" t="str">
+        <v>https://nswgame.com/angry-birds-trilogy-wii-u-download-free/</v>
+      </c>
+      <c r="C59" t="str">
+        <v>https://www.youtube.com/embed/gHraRhHE2FQ</v>
+      </c>
+      <c r="D59" t="str">
+        <v>imagenes/WII U/Angry Birds Trilogy.jpg</v>
+      </c>
+      <c r="E59" t="str">
+        <v>Duplicate comment detected; it looks as though you’ve already said that!</v>
+      </c>
+      <c r="F59" t="str">
+        <v>No</v>
+      </c>
+      <c r="I59" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J59" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K59" t="str">
+        <v>https://x.com/intent/post?text=Calm%20Down!%20Just%20go%20here%20USA:https://clk.sh/full?api=1a83dc23a...%20&amp;url=https%3A%2F%2Fnswgame.com%2Fangry-birds-trilogy-wii-u-download-free%2F%23comment-4496</v>
+      </c>
+      <c r="L59" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T59" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+      <c r="W59" t="str">
+        <v>https://1fichier.com/?imwpg6dg075md2kksr6m</v>
+      </c>
+      <c r="X59" t="str">
+        <v>https://1fichier.com/?dh2m9lg8627d7mw6dspl</v>
+      </c>
+      <c r="Y59" t="str">
+        <v>https://clk.sh/full?api=1a83dc23a56e37f8d4635da35fc71e6a9e912db2&amp;url=aHR0cHM6Ly8xZmljaGllci5jb20vPzBpaTVrMjloMTU5eG9yNXdrbndz&amp;type=2: https://1fichier.com/?0ii5k29h159xor5wknws</v>
+      </c>
+      <c r="Z59" t="str">
+        <v>https://clk.sh/full?api=1a83dc23a56e37f8d4635da35fc71e6a9e912db2&amp;url=aHR0cHM6Ly8xZmljaGllci5jb20vP2RiYWNoeXlvcHdjbjRtOTFud2Nj&amp;type=2: https://1fichier.com/?dbachyyopwcn4m91nwcc</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Angry Birds Star Wars</v>
+      </c>
+      <c r="B60" t="str">
+        <v>https://nswgame.com/angry-birds-star-wars-wii-u-download-free/</v>
+      </c>
+      <c r="C60" t="str">
+        <v>https://www.youtube.com/embed/sYrYokdwpAY</v>
+      </c>
+      <c r="D60" t="str">
+        <v>imagenes/WII U/Angry Birds Star Wars.jpg</v>
+      </c>
+      <c r="E60" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F60" t="str">
+        <v>No</v>
+      </c>
+      <c r="I60" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T60" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>LEGO Batman ﻿2 DC Super Heroes</v>
+      </c>
+      <c r="B61" t="str">
+        <v>https://nswgame.com/%ef%bb%bflego-batman-%ef%bb%bf2-dc-super-heroes%ef%bb%bf-wii-u-download-free/</v>
+      </c>
+      <c r="C61" t="str">
+        <v>https://www.youtube.com/embed/FvJMqwN5V4Q</v>
+      </c>
+      <c r="D61" t="str">
+        <v>imagenes/WII U/LEGO Batman ﻿2 DC Super Heroes.jpg</v>
+      </c>
+      <c r="E61" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F61" t="str">
+        <v>No</v>
+      </c>
+      <c r="I61" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T61" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+    </row>
+    <row r="62" xml:space="preserve">
+      <c r="A62" t="str">
+        <v>Mighty No 9</v>
+      </c>
+      <c r="B62" t="str">
+        <v>https://nswgame.com/mighty-no-9%ef%bb%bf-wii-u-download-free/</v>
+      </c>
+      <c r="C62" t="str">
+        <v>https://www.youtube.com/embed/fFSl-fS9grQ</v>
+      </c>
+      <c r="D62" t="str">
+        <v>imagenes/WII U/Mighty No 9.jpg</v>
+      </c>
+      <c r="E62" t="str" xml:space="preserve">
+        <v xml:space="preserve">Mighty No. 9 is an all-new Japanese side-scrolling action game that takes the best aspects of the 8- and 16-bit era classics you know and love, and transforms them with modern tech, fresh mechanics, and fan input into something fresh and amazing!
+You play as Beck, the 9th in a line of powerful robots, and the only one not infected by a mysterious computer virus that has caused mechanized creatures the world over to go berserk. Run, jump, blast, and transform your way through six stages (or more, via stretch goals) you can tackle in any order you choose, using weapons and abilities stolen from your enemies to take down your fellow Mighty Number robots and confront the final evil that threatens the planet!
+Once, you worked together, side-by-side but now, your fellow Mighty No. robots have lashed out, taking over key strategic locations across the globe and infesting them with their minions. You have no choice: the other Mighty Numbers…Must. Be. Destroyed!
+But it wont be easy. Although they were originally designed for industrial purposes, the Mighty Numbers have all become fierce warriors, seasoned through seasons in the most popular spectator sport of the future: robot-on-robot combat in the Battle Colosseo!</v>
+      </c>
+      <c r="F62" t="str">
+        <v>No</v>
+      </c>
+      <c r="I62" t="str">
+        <v>https://filecrypt.cc/Container/D9D1F38B57.html</v>
+      </c>
+      <c r="J62" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="K62" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="L62" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T62" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Mario Tennis Ultra Smash</v>
+      </c>
+      <c r="B63" t="str">
+        <v>https://nswgame.com/mario-tennis-ultra-smash-wii-u-download-free/</v>
+      </c>
+      <c r="C63" t="str">
+        <v>https://www.youtube.com/embed/PXBWAjxioSU</v>
+      </c>
+      <c r="D63" t="str">
+        <v>imagenes/WII U/Mario Tennis Ultra Smash.jpg</v>
+      </c>
+      <c r="E63" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F63" t="str">
+        <v>No</v>
+      </c>
+      <c r="G63" t="str">
+        <v>https://mega.nz/#!6OYxgZTI!tScldtz-8oVdFfh7oi9HiWEFhyxf_SWqBoisdGnGwAo</v>
+      </c>
+      <c r="H63" t="str">
+        <v>https://1fichier.com/?6dzyojpm0j&amp;af=62851</v>
+      </c>
+      <c r="I63" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J63" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K63" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T63" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+    </row>
+    <row r="64" xml:space="preserve">
+      <c r="A64" t="str">
+        <v>Mario Party 10</v>
+      </c>
+      <c r="B64" t="str">
+        <v>https://nswgame.com/mario-party-10-wii-u-download-free/</v>
+      </c>
+      <c r="C64" t="str">
+        <v>https://www.youtube.com/embed/L69Z39bgdU4</v>
+      </c>
+      <c r="D64" t="str">
+        <v>imagenes/WII U/Mario Party 10.jpg</v>
+      </c>
+      <c r="E64" t="str" xml:space="preserve">
+        <v xml:space="preserve">I checked and they’re fine, new megaup links are up though ^^
+Please reupload in another way, mega have limited mbs.
+the mediafire files are deleted, can you reupload please ?</v>
+      </c>
+      <c r="F64" t="str">
+        <v>Sí</v>
+      </c>
+      <c r="I64" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J64" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K64" t="str">
+        <v>https://nswgame.com/running-fable-petite-party-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+      <c r="L64" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="W64" t="str">
+        <v>https://1fichier.com/?gxi08mfjii6kq1wyjwmk</v>
+      </c>
+      <c r="X64" t="str">
+        <v>https://1fichier.com/?oyl2z9hm8bhugc1g8dxn</v>
+      </c>
+      <c r="AD64" t="str">
+        <v>https://megaup.net/2cvyZ/MP10-USA-LOADIINE-ZIPERTO.rar</v>
+      </c>
+      <c r="AE64" t="str">
+        <v>https://megaup.net/2cvx3/MP10-USA-LOADIINE-UPDATE-ZIPERTO.rar</v>
+      </c>
+    </row>
+    <row r="65" xml:space="preserve">
+      <c r="A65" t="str">
+        <v>Mario Kart 8</v>
+      </c>
+      <c r="B65" t="str">
+        <v>https://nswgame.com/mario-kart-8-wii-u-download-free/</v>
+      </c>
+      <c r="C65" t="str">
+        <v>https://www.youtube.com/embed/g2cCq0PaNck</v>
+      </c>
+      <c r="D65" t="str">
+        <v>imagenes/WII U/Mario Kart 8.jpg</v>
+      </c>
+      <c r="E65" t="str" xml:space="preserve">
+        <v xml:space="preserve">If I want to start the game cemu is allways crshing. What can I do?
+I don’t really know much about this so I’ll let others help you :((
+File &gt; Instal game or Update DLC look for the Meta File.</v>
+      </c>
+      <c r="F65" t="str">
+        <v>No</v>
+      </c>
+      <c r="I65" t="str">
+        <v>https://www.filecrypt.cc/Container/542C1E3864.html</v>
+      </c>
+      <c r="J65" t="str">
+        <v>https://send.now/d/8p4N</v>
+      </c>
+      <c r="K65" t="str">
+        <v>https://send.now/d/8p4D</v>
+      </c>
+      <c r="L65" t="str">
+        <v>https://www.filecrypt.cc/Container/4A29F25061.html</v>
+      </c>
+      <c r="M65" t="str">
+        <v>https://ziperto.download/Files/WII%20U/MK8-WII%20U-SC-ZIPERTO.rar</v>
+      </c>
+      <c r="N65" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="Q65" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="R65" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T65" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+      <c r="W65" t="str">
+        <v>https://1fichier.com/?qizx488hbze9a49g33kq</v>
+      </c>
+      <c r="X65" t="str">
+        <v>https://1fichier.com/?echfb6jfuzrhaixeucx7&amp;af=62851</v>
+      </c>
+      <c r="Y65" t="str">
+        <v>https://1fichier.com/?q7lcs0w31zg3oi3u9bn9&amp;af=62851</v>
+      </c>
+      <c r="Z65" t="str">
+        <v>https://1fichier.com/?qgsdtmydohx5gq4p0fh2: https://1fichier.com/?qgsdtmydohx5gq4p0fh2</v>
+      </c>
+      <c r="AD65" t="str">
+        <v>https://megaup.net/12izk/MK8-USA-UP64-LOADIINE-Ziperto.rar</v>
+      </c>
+      <c r="AE65" t="str">
+        <v>https://megaup.net/12izn/MK8-USA-DLCs-LOADIINE-ZIPERTO.rar</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>LEGO The Hobbit</v>
+      </c>
+      <c r="B66" t="str">
+        <v>https://nswgame.com/lego-the-hobbit-wii-u-download-free/</v>
+      </c>
+      <c r="C66" t="str">
+        <v>https://www.youtube.com/embed/Ywy0tkQnUKQ</v>
+      </c>
+      <c r="D66" t="str">
+        <v>imagenes/WII U/LEGO The Hobbit.jpg</v>
+      </c>
+      <c r="E66" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F66" t="str">
+        <v>No</v>
+      </c>
+      <c r="I66" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T66" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+    </row>
+    <row r="67" xml:space="preserve">
+      <c r="A67" t="str">
+        <v>LEGO Star Wars The Force Awakens</v>
+      </c>
+      <c r="B67" t="str">
+        <v>https://nswgame.com/lego-star-wars-the-force-awakens-wii-u-download-free/</v>
+      </c>
+      <c r="C67" t="str">
+        <v>https://www.youtube.com/embed/HZzvGihbeB8</v>
+      </c>
+      <c r="D67" t="str">
+        <v>imagenes/WII U/LEGO Star Wars The Force Awakens.jpg</v>
+      </c>
+      <c r="E67" t="str" xml:space="preserve">
+        <v xml:space="preserve">File format is different from other files
+In other words, the file is wrong.
+The file is not available on the device.
+It was confirmed after decompression.
+Did you find the right game? This one is for Wii U, also if the file from Mega link didn’t work, try 1fichier one :((
+I’ll go in and understand where you’ve told me.
+I don’t know if I can do it.
+Thank you very much for letting me know.</v>
+      </c>
+      <c r="F67" t="str">
+        <v>No</v>
+      </c>
+      <c r="H67" t="str">
+        <v>https://1fichier.com/?5nx78c6h3ayaclp0695s</v>
+      </c>
+      <c r="I67" t="str">
+        <v>https://www.filecrypt.cc/Container/605D7B7E21.html</v>
+      </c>
+      <c r="J67" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="K67" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="L67" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T67" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>LEGO Marvels Avengers</v>
+      </c>
+      <c r="B68" t="str">
+        <v>https://nswgame.com/lego-marvels-avengers-wii-u-download-free/</v>
+      </c>
+      <c r="C68" t="str">
+        <v>https://www.youtube.com/embed/3C09w9aDAWY</v>
+      </c>
+      <c r="D68" t="str">
+        <v>imagenes/WII U/LEGO Marvels Avengers.jpg</v>
+      </c>
+      <c r="E68" t="str">
+        <v>Hello, can you reupload the last part (4) of the game? Tnx</v>
+      </c>
+      <c r="F68" t="str">
+        <v>No</v>
+      </c>
+      <c r="H68" t="str">
+        <v>https://1fichier.com/?rkxznhiv3r&amp;af=62851: https://1fichier.com/?rkxznhiv3r&amp;af=62851</v>
+      </c>
+      <c r="I68" t="str">
+        <v>https://www.filecrypt.cc/Container/2D83BAFD62.html</v>
+      </c>
+      <c r="J68" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="K68" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="L68" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T68" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>LEGO Jurassic World</v>
+      </c>
+      <c r="B69" t="str">
+        <v>https://nswgame.com/lego-jurassic-world-wii-u-download-free/</v>
+      </c>
+      <c r="C69" t="str">
+        <v>https://www.youtube.com/embed/ABZb9NaFBxM</v>
+      </c>
+      <c r="D69" t="str">
+        <v>imagenes/WII U/LEGO Jurassic World.jpg</v>
+      </c>
+      <c r="E69" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F69" t="str">
+        <v>No</v>
+      </c>
+      <c r="I69" t="str">
+        <v>https://www.filecrypt.cc/Container/0532510A9D.html</v>
+      </c>
+      <c r="J69" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="K69" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="L69" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T69" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+    </row>
+    <row r="70" xml:space="preserve">
+      <c r="A70" t="str">
+        <v>LEGO Dimension﻿s</v>
+      </c>
+      <c r="B70" t="str">
+        <v>https://nswgame.com/lego-dimension%ef%bb%bfs-wii-u-download-free/</v>
+      </c>
+      <c r="C70" t="str">
+        <v>https://www.youtube.com/embed/idKrdkjEXjE</v>
+      </c>
+      <c r="D70" t="str">
+        <v>imagenes/WII U/LEGO Dimension﻿s.jpg</v>
+      </c>
+      <c r="E70" t="str" xml:space="preserve">
+        <v xml:space="preserve">The game links are dead, 404 Not Found. The update/dlc still seem fine. Please reupload
+While it seems the links are working now, the issue is this is NOT the USA version of the game. This is the EUR version. On top of that, its a bad dump of the EUR version (it loads, but cemu labels it as a bad dump). I already have a good dump of EUR version from elsewhere. The USA version seems impossible to find.
+Can you upload in a google drive, the game, update and dlc, please?</v>
+      </c>
+      <c r="F70" t="str">
+        <v>No</v>
+      </c>
+      <c r="I70" t="str">
+        <v>https://www.filecrypt.cc/Container/670647A6F7.html</v>
+      </c>
+      <c r="J70" t="str">
+        <v>https://www.filecrypt.cc/Container/90D37EDCB1.html</v>
+      </c>
+      <c r="K70" t="str">
+        <v>https://www.filecrypt.cc/Container/FF9933BD85.html</v>
+      </c>
+      <c r="L70" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="M70" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="N70" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T70" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+      <c r="W70" t="str">
+        <v>https://x.com/intent/post?text=https://1fichier.com/?56rjv51t1bjsnisfcqi7&amp;af=62851...%20&amp;url=https%3A%2F%2Fnswgame.com%2Flego-dimension%25ef%25bb%25bfs-wii-u-download-free%2F%23comment-10427</v>
+      </c>
+      <c r="X70" t="str">
+        <v>https://1fichier.com/?56rjv51t1bjsnisfcqi7&amp;af=62851: https://1fichier.com/?56rjv51t1bjsnisfcqi7&amp;af=62851</v>
+      </c>
+      <c r="Y70" t="str">
+        <v>https://1fichier.com/?orye7numv5pas0o0uon9&amp;af=62851: https://1fichier.com/?orye7numv5pas0o0uon9&amp;af=62851</v>
+      </c>
+      <c r="Z70" t="str">
+        <v>https://1fichier.com/?6t3af1q83j6kp0tvwsby&amp;af=62851: https://1fichier.com/?6t3af1q83j6kp0tvwsby&amp;af=62851</v>
+      </c>
+      <c r="AF70" t="str">
+        <v>https://x.com/intent/post?text=I%20have%20some%20DLC%20files%20here:%20https://mega.nz/#F!CfpUgYpS!H...%20&amp;url=https%3A%2F%2Fnswgame.com%2Flego-dimension%25ef%25bb%25bfs-wii-u-download-free%2F%23comment-1526</v>
+      </c>
+      <c r="AG70" t="str">
+        <v>https://mega.nz/#F!CfpUgYpS!Hz1OBYS5ublwq7xCYtg61Q: https://mega.nz/#F!CfpUgYpS!Hz1OBYS5ublwq7xCYtg61Q</v>
+      </c>
+    </row>
+    <row r="71" xml:space="preserve">
+      <c r="A71" t="str">
+        <v>LEGO City Undercover</v>
+      </c>
+      <c r="B71" t="str">
+        <v>https://nswgame.com/lego-city-undercover%ef%bb%bf%ef%bb%bf-wii-u-download-free/</v>
+      </c>
+      <c r="C71" t="str">
+        <v>https://www.youtube.com/embed/aByXOzLbsao</v>
+      </c>
+      <c r="D71" t="str">
+        <v>imagenes/WII U/LEGO City Undercover.jpg</v>
+      </c>
+      <c r="E71" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi,
+I tried every title key and didn’t work.
+Is there a specific key for this rom?</v>
+      </c>
+      <c r="F71" t="str">
+        <v>No</v>
+      </c>
+      <c r="H71" t="str">
+        <v>https://1fichier.com/?soys1le4tlzl5t79bqt6</v>
+      </c>
+      <c r="I71" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J71" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K71" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T71" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+    </row>
+    <row r="72" xml:space="preserve">
+      <c r="A72" t="str">
+        <v>LEGO Batman 3 Beyond Gotham</v>
+      </c>
+      <c r="B72" t="str">
+        <v>https://nswgame.com/lego-batman-3-beyond-gotham-wii-u-download-free/</v>
+      </c>
+      <c r="C72" t="str">
+        <v>https://www.youtube.com/embed/w7nS796Gt2M</v>
+      </c>
+      <c r="D72" t="str">
+        <v>imagenes/WII U/LEGO Batman 3 Beyond Gotham.jpg</v>
+      </c>
+      <c r="E72" t="str" xml:space="preserve">
+        <v xml:space="preserve">In LEGO Batman 3: Beyond Gotham, the Caped Crusader joins forces with the super heroes of the DC Comics universe and blasts off to outer space to stop the evil Brainiac from destroying Earth.
+The best-selling LEGO Batman videogame franchise returns in an out-of-this-world, action-packed adventure! In LEGO Batman 3: Beyond Gotham, the Caped Crusader joins forces with the super heroes of the DC Comics universe and blasts off to outer space to stop the evil Brainiac from destroying Earth.
+Using the power of the Lantern Rings, Brainiac shrinks worlds to add to his twisted collection of miniature cities from across the universe. Now the greatest super heroes and the most cunning villains must unite and journey to different Lantern Worlds to collect the Lantern Rings and stop Brainiac before its too late.</v>
+      </c>
+      <c r="F72" t="str">
+        <v>No</v>
+      </c>
+      <c r="I72" t="str">
+        <v>https://www.filecrypt.cc/Container/DA8749B4DE.html</v>
+      </c>
+      <c r="J72" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="K72" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="L72" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T72" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+    </row>
+    <row r="73" xml:space="preserve">
+      <c r="A73" t="str">
+        <v>Kirby and the Rainbow Paintbrush</v>
+      </c>
+      <c r="B73" t="str">
+        <v>https://nswgame.com/kirby-and-the-rainbow-paintbrush-wii-u-download-free/</v>
+      </c>
+      <c r="C73" t="str">
+        <v>https://www.youtube.com/embed/VFlZBGgtsWs</v>
+      </c>
+      <c r="D73" t="str">
+        <v>imagenes/WII U/Kirby and the Rainbow Paintbrush.jpg</v>
+      </c>
+      <c r="E73" t="str" xml:space="preserve">
+        <v xml:space="preserve">Do you have the magic touch? Then guide Kirby as he sets off on grand adventures in a hand-sculpted clay world. Draw lines on the touch screen of the Wii U GamePad controller to create rainbow-colored clay ropes to move Kirby around freely, or tap him to attack enemies or blast through obstacles. Transformations include a submarine, rocket and tank. In underwater levels, Kirby dons a swim mask. If his power level gets too low, a clay bandage
+appears on his head.</v>
+      </c>
+      <c r="F73" t="str">
+        <v>No</v>
+      </c>
+      <c r="I73" t="str">
+        <v>https://filecrypt.cc/Container/B4909232C8.html</v>
+      </c>
+      <c r="J73" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="K73" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="L73" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T73" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+    </row>
+    <row r="74" xml:space="preserve">
+      <c r="A74" t="str">
+        <v>Kirby and the Rainbow Curse</v>
+      </c>
+      <c r="B74" t="str">
+        <v>https://nswgame.com/kirby-and-the-rainbow-curse-wii-u-download-free/</v>
+      </c>
+      <c r="C74" t="str">
+        <v>https://www.youtube.com/embed/D0uLgdlEBbk</v>
+      </c>
+      <c r="D74" t="str">
+        <v>imagenes/WII U/Kirby and the Rainbow Curse.jpg</v>
+      </c>
+      <c r="E74" t="str" xml:space="preserve">
+        <v xml:space="preserve">Do you have the magic touch? Then guide Kirby as he sets off on grand adventures in a hand-sculpted clay world. Draw lines on the touch screen of the Wii U GamePad controller to create rainbow-colored clay ropes to move Kirby around freely, or tap him to attack enemies or blast through obstacles. Transformations include a submarine, rocket and tank. In underwater levels, Kirby dons a swim mask. If his power level gets too low, a clay bandage
+appears on his head.
+This page is stupid cuz it sends me to a page where you can book a hotel! I mean WHYYYYYYYYYY???? JUST SEND A LINK OF THE FILE WITH MEGA.NZ !!!
+Couldn’t find other links for it ToT But new links for LOADIINE version are up, maybe it can help :((</v>
+      </c>
+      <c r="F74" t="str">
+        <v>No</v>
+      </c>
+      <c r="H74" t="str">
+        <v>https://1fichier.com/?7v06j2njtxibodhuc2oa</v>
+      </c>
+      <c r="I74" t="str">
+        <v>https://filecrypt.co/Container/128BEAB71A.html</v>
+      </c>
+      <c r="J74" t="str">
+        <v>https://www.filecrypt.cc/Container/F893D07D1C.html</v>
+      </c>
+      <c r="K74" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="L74" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="M74" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T74" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Just Dance Kids 2014</v>
+      </c>
+      <c r="B75" t="str">
+        <v>https://nswgame.com/just-dance-kids-2014-wii-u-download-free/</v>
+      </c>
+      <c r="C75" t="str">
+        <v>https://www.youtube.com/embed/6vOzyim1Chs</v>
+      </c>
+      <c r="D75" t="str">
+        <v>imagenes/WII U/Just Dance Kids 2014.jpg</v>
+      </c>
+      <c r="E75" t="str">
+        <v>Now, the coolest dance experience for kids is back, Just Dance Kids 2014 is now on Wii and Wii U! Featuring over 30 fun and crazy dance routines to kids favorite songs, including hits from todays most popular artists, TV shows and movies. Just Dance Kids 2014 gets kids of all ages up and dancing with colorful graphics, super-fun dance moves, and kid-friendly gameplay</v>
+      </c>
+      <c r="F75" t="str">
+        <v>No</v>
+      </c>
+      <c r="I75" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Just Dance Disney Party 2</v>
+      </c>
+      <c r="B76" t="str">
+        <v>https://nswgame.com/just-dance-disney-party-2-wii-u-download-free/</v>
+      </c>
+      <c r="C76" t="str">
+        <v>https://www.youtube.com/embed/4TbiMTESqlQ</v>
+      </c>
+      <c r="D76" t="str">
+        <v>imagenes/WII U/Just Dance Disney Party 2.jpg</v>
+      </c>
+      <c r="E76" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F76" t="str">
+        <v>No</v>
+      </c>
+      <c r="I76" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J76" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K76" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T76" t="str">
+        <v>https://drive.google.com/file/d/1UsdnIGvssmenCKB6s1Sz-jeRoKnwXseO/view</v>
+      </c>
+      <c r="W76" t="str">
+        <v>https://1fichier.com/?56lu0b6qkg3ujhh2vffc</v>
+      </c>
+      <c r="X76" t="str">
+        <v>https://1fichier.com/?kqnqn47gaqq5i3gw4gbd</v>
+      </c>
+    </row>
+    <row r="77" xml:space="preserve">
+      <c r="A77" t="str">
+        <v>Just Dance 2016</v>
+      </c>
+      <c r="B77" t="str">
+        <v>https://nswgame.com/just-dance-2016-wii-u-download-free/</v>
+      </c>
+      <c r="C77" t="str">
+        <v>https://www.youtube.com/embed/_ZTmanCij6g</v>
+      </c>
+      <c r="D77" t="str">
+        <v>imagenes/WII U/Just Dance 2016.jpg</v>
+      </c>
+      <c r="E77" t="str" xml:space="preserve">
+        <v xml:space="preserve">Introducing Just Dance 2016 – the newest game from the top-selling franchise – with a brand new way to play! All you need is your smartphone and the Just Dance Controller App to play Just Dance 2016 on PS4 system, no PlayStationCamera or PlayStationMove needed.
+Bust a move to Uptown Funk by Mark Ronson Ft. Bruno Mars and feel the beat in All About That Bass by Meghan Trainor – Just Dance 2016 features an amazing tracklist with visuals that are more creative and breath-taking than ever before. Join over 100MM players and dance to fun favorites and hot hits, today!</v>
+      </c>
+      <c r="F77" t="str">
+        <v>No</v>
+      </c>
+      <c r="I77" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J77" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K77" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="W77" t="str">
+        <v>https://1fichier.com/?bran5jesmxu70119gx92</v>
+      </c>
+      <c r="X77" t="str">
+        <v>https://1fichier.com/?irpe8mw3pzmm3r2nxyn7</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>Just Dance 2015</v>
+      </c>
+      <c r="B78" t="str">
+        <v>https://nswgame.com/just-dance-2015-wii-u-download-free/</v>
+      </c>
+      <c r="C78" t="str">
+        <v>https://www.youtube.com/embed/clmcARFqxl4</v>
+      </c>
+      <c r="D78" t="str">
+        <v>imagenes/WII U/Just Dance 2015.jpg</v>
+      </c>
+      <c r="E78" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F78" t="str">
+        <v>No</v>
+      </c>
+      <c r="I78" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="J78" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="K78" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="W78" t="str">
+        <v>https://1fichier.com/?r2vkcvj2u9dxsvw3h0zi</v>
+      </c>
+      <c r="X78" t="str">
+        <v>https://1fichier.com/?1ku1qr9th5d4wdqxm2oj</v>
+      </c>
+    </row>
+    <row r="79" xml:space="preserve">
+      <c r="A79" t="str">
+        <v>Hyrule Warriors</v>
+      </c>
+      <c r="B79" t="str">
+        <v>https://nswgame.com/hyrule-warriors-wii-u-download-free/</v>
+      </c>
+      <c r="C79" t="str">
+        <v>https://www.youtube.com/embed/2c8EEXL3L8c</v>
+      </c>
+      <c r="D79" t="str">
+        <v>imagenes/WII U/Hyrule Warriors.jpg</v>
+      </c>
+      <c r="E79" t="str" xml:space="preserve">
+        <v xml:space="preserve">The delicate balance of the Triforce has been disrupted, and Hyrule Kingdom is once again being torn apart by a dark power, this time lead by Sorceress Cia. Now its up to the legendary hero Link to face hordes of enemies and find the missing Princess Zelda. Advance the story to unlock new playable characters with unique moves and weapon types. Collect Rupees and other useful items to upgrade weapons and craft badges, which you can use to bolster each warriors abilities. Then unleash the full power of your attacks with intense combos to clear wave after wave of Bokoblin hordes. Youll have to get your gloves dirty to save Hyrule this time.
+* Play as fan-favorite characters like Link and Impa for the first time in the series!
+* Battle the fiercest Legend of Zelda enemies across Hyrules most famous locales.
+* Lay waste to your opponents with brutally efficient attacks and intense combos
+* Think tactically and complete missions in the most efficient way possible
+Good news is that we found mega links for the game, bad news is that they don’t include update and dlc :((</v>
+      </c>
+      <c r="F79" t="str">
+        <v>No</v>
+      </c>
+      <c r="I79" t="str">
+        <v>https://www.filecrypt.cc/Container/758FCB7D17.html</v>
+      </c>
+      <c r="J79" t="str">
+        <v>https://www.filecrypt.cc/Container/511C145B53.html</v>
+      </c>
+      <c r="K79" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="L79" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="M79" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T79" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+      <c r="W79" t="str">
+        <v>https://1fichier.com/?zvrphz4fcnb8dbbh5gxh</v>
+      </c>
+      <c r="X79" t="str">
+        <v>https://1fichier.com/?d2a68g2911oo4i56cfuj</v>
+      </c>
+      <c r="AD79" t="str">
+        <v>https://megaup.net/4Tz6y/HW-USA-UPDATE-LOADIINE-ZIPERTO.rar</v>
+      </c>
+      <c r="AE79" t="str">
+        <v>https://megaup.net/4dBD0/HW-USA-DLC-LOADIINE-ZIPERTO.rar</v>
+      </c>
+    </row>
+    <row r="80" xml:space="preserve">
+      <c r="A80" t="str">
+        <v>Hot Wheels Worlds Best Driver</v>
+      </c>
+      <c r="B80" t="str">
+        <v>https://nswgame.com/hot-wheels-worlds-best-driver-wii-u-download-free/</v>
+      </c>
+      <c r="C80" t="str">
+        <v>https://www.youtube.com/embed/QG_2MKcunxQ</v>
+      </c>
+      <c r="D80" t="str">
+        <v>imagenes/WII U/Hot Wheels Worlds Best Driver.jpg</v>
+      </c>
+      <c r="E80" t="str" xml:space="preserve">
+        <v xml:space="preserve">Do you have what it takes to be the World’s Best Driver?
+Gear up for the most intense challenges only Hot Wheels can deliver! Pick your team, choose your ride and go for it! Get behind the wheel of thrilling Hot Wheels vehicles while joining the elite ranks of Team Hot Wheels. Compete in dozens of unique, fast-paced, re-playable challenges all highlighting the different driving styles of Team Hot Wheels: the speed record-breaking Green Team, the show-stopping stunts of the Red Team, the high-tech precision of the Blue Team and the world record-breaking jumps of the Yellow Team. Do you have what it takes to be the World’s Best Driver?
+So sorry, we could only find 1fichier link for this game :((</v>
+      </c>
+      <c r="F80" t="str">
+        <v>No</v>
+      </c>
+      <c r="I80" t="str">
+        <v>https://www.filecrypt.cc/Container/1510D3D699.html</v>
+      </c>
+      <c r="J80" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="K80" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="L80" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T80" t="str">
+        <v>https://nswgame.com/drive-rally-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>Game &amp; W﻿ario</v>
+      </c>
+      <c r="B81" t="str">
+        <v>https://nswgame.com/game-w%ef%bb%bfario%ef%bb%bf%ef%bb%bf-wii-u-download-free/</v>
+      </c>
+      <c r="C81" t="str">
+        <v>https://www.youtube.com/embed/pHWn2oJbZH4</v>
+      </c>
+      <c r="D81" t="str">
+        <v>imagenes/WII U/Game &amp; W﻿ario.jpg</v>
+      </c>
+      <c r="E81" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F81" t="str">
+        <v>Sí</v>
+      </c>
+      <c r="I81" t="str">
+        <v>https://www.filecrypt.cc/Container/603688F902.html</v>
+      </c>
+      <c r="J81" t="str">
+        <v>https://nswgame.com/guide-download-game/</v>
+      </c>
+      <c r="K81" t="str">
+        <v>https://nswgame.com/guide-download-game-use-jdownload/</v>
+      </c>
+      <c r="L81" t="str">
+        <v>https://nswgame.com/running-fable-petite-party-nintendo-switch-nsp-xci-nsz-download-free/</v>
+      </c>
+      <c r="M81" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AP41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AG81"/>
   </ignoredErrors>
 </worksheet>
 </file>